--- a/data/all_datasets/REDD/REDD_House6_stats/2026-04-18.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-04-18.xlsx
@@ -463,7 +463,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="3">
@@ -496,7 +496,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="7">
@@ -518,7 +518,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
@@ -529,7 +529,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="9">
@@ -551,7 +551,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="11">
@@ -573,7 +573,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="13">
@@ -584,7 +584,7 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="14">
@@ -606,7 +606,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="16">
@@ -617,7 +617,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="17">
@@ -628,7 +628,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="18">
@@ -639,7 +639,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="19">
@@ -650,7 +650,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="20">
@@ -661,7 +661,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="21">
@@ -672,7 +672,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="22">
@@ -683,7 +683,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="23">
@@ -702,10 +702,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1176470588235294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -713,10 +713,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
   </sheetData>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.488341890945037</v>
+        <v>12.89524890142427</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5079166025670946</v>
+        <v>0.6722812451752744</v>
       </c>
     </row>
     <row r="3">
@@ -773,7 +773,7 @@
         <v>1.989561867182847</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1557457238168704</v>
+        <v>0.1037238706788512</v>
       </c>
     </row>
     <row r="4">
@@ -786,7 +786,7 @@
         <v>1.288033589291611</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1008290955780705</v>
+        <v>0.06715037699977257</v>
       </c>
     </row>
     <row r="5">
@@ -799,7 +799,7 @@
         <v>1.238843897306535</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09697845674702346</v>
+        <v>0.06458592030488369</v>
       </c>
     </row>
     <row r="6">
@@ -812,7 +812,7 @@
         <v>0.9967506106026892</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07802705101753764</v>
+        <v>0.05196462253250338</v>
       </c>
     </row>
     <row r="7">
@@ -825,7 +825,7 @@
         <v>0.7728918554771155</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06050307027340335</v>
+        <v>0.04029396430871482</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.488341890945037</v>
+        <v>12.89524890142427</v>
       </c>
     </row>
     <row r="3">
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1141,7 +1141,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1187,7 +1187,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1325,7 +1325,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -1555,7 +1555,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -1693,7 +1693,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -1739,7 +1739,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1969,7 +1969,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -5143,7 +5143,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -5166,7 +5166,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -5189,7 +5189,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -5235,7 +5235,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -5327,7 +5327,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -5350,7 +5350,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -5373,7 +5373,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -5396,7 +5396,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -5442,7 +5442,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -5511,7 +5511,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -5534,7 +5534,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
@@ -5557,7 +5557,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -5603,7 +5603,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
@@ -5626,7 +5626,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
@@ -5672,7 +5672,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
@@ -5718,7 +5718,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
@@ -5787,7 +5787,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
@@ -5810,7 +5810,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
@@ -5833,7 +5833,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
@@ -5856,7 +5856,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
@@ -5902,7 +5902,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -5971,7 +5971,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
@@ -5994,7 +5994,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
@@ -6040,7 +6040,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
@@ -6063,7 +6063,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C223" t="n">
         <v>0</v>
@@ -6086,7 +6086,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
@@ -6109,7 +6109,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -6178,7 +6178,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -6224,7 +6224,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -6247,7 +6247,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
@@ -6270,7 +6270,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -6316,7 +6316,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -6385,7 +6385,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -6431,7 +6431,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -6477,7 +6477,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
@@ -7535,7 +7535,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C288" t="n">
         <v>0</v>
@@ -7581,7 +7581,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C289" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C290" t="n">
         <v>0</v>
@@ -7627,7 +7627,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C291" t="n">
         <v>0</v>
@@ -7650,7 +7650,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C292" t="n">
         <v>0</v>
@@ -7673,7 +7673,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C293" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C294" t="n">
         <v>0</v>
@@ -7719,7 +7719,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C295" t="n">
         <v>0</v>
@@ -7742,7 +7742,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C296" t="n">
         <v>0</v>
@@ -7765,7 +7765,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C297" t="n">
         <v>0</v>
@@ -7788,7 +7788,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C298" t="n">
         <v>0</v>
@@ -7811,7 +7811,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C299" t="n">
         <v>0</v>
@@ -7834,7 +7834,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C300" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C301" t="n">
         <v>0</v>
@@ -10295,7 +10295,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C407" t="n">
         <v>102.8814692633022</v>
@@ -10318,7 +10318,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C408" t="n">
         <v>102.8814692633022</v>
@@ -10341,7 +10341,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C409" t="n">
         <v>102.8814692633022</v>
@@ -10364,7 +10364,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C410" t="n">
         <v>102.8814692633022</v>
@@ -10387,7 +10387,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C411" t="n">
         <v>102.8814692633022</v>
@@ -10410,7 +10410,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C412" t="n">
         <v>102.8814692633022</v>
@@ -10433,7 +10433,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C413" t="n">
         <v>102.8814692633022</v>
@@ -10456,7 +10456,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C414" t="n">
         <v>102.8814692633022</v>
@@ -10479,7 +10479,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C415" t="n">
         <v>102.8814692633022</v>
@@ -10502,7 +10502,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C416" t="n">
         <v>102.8814692633022</v>
@@ -10525,7 +10525,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C417" t="n">
         <v>102.8814692633022</v>
@@ -10548,7 +10548,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C418" t="n">
         <v>102.8814692633022</v>
@@ -10571,7 +10571,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C419" t="n">
         <v>102.8814692633022</v>
@@ -10594,7 +10594,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C420" t="n">
         <v>102.8814692633022</v>
@@ -10617,7 +10617,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C421" t="n">
         <v>102.8814692633022</v>
@@ -10640,7 +10640,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C422" t="n">
         <v>102.8814692633022</v>
@@ -10663,7 +10663,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C423" t="n">
         <v>102.8814692633022</v>
@@ -10686,7 +10686,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C424" t="n">
         <v>102.8814692633022</v>
@@ -10709,7 +10709,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C425" t="n">
         <v>102.8814692633022</v>
@@ -10732,7 +10732,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C426" t="n">
         <v>102.8814692633022</v>
@@ -10755,7 +10755,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C427" t="n">
         <v>102.8814692633022</v>
@@ -10778,7 +10778,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C428" t="n">
         <v>102.8814692633022</v>
@@ -10801,7 +10801,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C429" t="n">
         <v>102.8814692633022</v>
@@ -10824,7 +10824,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C430" t="n">
         <v>102.8814692633022</v>
@@ -10847,7 +10847,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C431" t="n">
         <v>102.8814692633022</v>
@@ -10870,7 +10870,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C432" t="n">
         <v>102.8814692633022</v>
@@ -10893,7 +10893,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C433" t="n">
         <v>102.8814692633022</v>
@@ -10916,7 +10916,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C434" t="n">
         <v>102.8814692633022</v>
@@ -10939,7 +10939,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C435" t="n">
         <v>102.8814692633022</v>
@@ -10962,7 +10962,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C436" t="n">
         <v>102.8814692633022</v>
@@ -10985,7 +10985,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C437" t="n">
         <v>102.8814692633022</v>
@@ -11008,7 +11008,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C438" t="n">
         <v>102.8814692633022</v>
@@ -11031,7 +11031,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C439" t="n">
         <v>102.8814692633022</v>
@@ -11054,7 +11054,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C440" t="n">
         <v>102.8814692633022</v>
@@ -11077,7 +11077,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C441" t="n">
         <v>102.8814692633022</v>
@@ -11100,7 +11100,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C442" t="n">
         <v>102.8814692633022</v>
@@ -11123,7 +11123,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C443" t="n">
         <v>102.8814692633022</v>
@@ -11146,7 +11146,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C444" t="n">
         <v>102.8814692633022</v>
@@ -11169,7 +11169,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C445" t="n">
         <v>102.8814692633022</v>
@@ -11192,7 +11192,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C446" t="n">
         <v>102.8814692633022</v>
@@ -11215,7 +11215,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C447" t="n">
         <v>102.8814692633022</v>
@@ -11238,7 +11238,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C448" t="n">
         <v>102.8814692633022</v>
@@ -11261,7 +11261,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C449" t="n">
         <v>102.8814692633022</v>
@@ -11284,7 +11284,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C450" t="n">
         <v>102.8814692633022</v>
@@ -11307,7 +11307,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C451" t="n">
         <v>102.8814692633022</v>
@@ -11330,7 +11330,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C452" t="n">
         <v>102.8814692633022</v>
@@ -11353,7 +11353,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C453" t="n">
         <v>102.8814692633022</v>
@@ -11376,7 +11376,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C454" t="n">
         <v>102.8814692633022</v>
@@ -11399,7 +11399,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C455" t="n">
         <v>102.8814692633022</v>
@@ -11422,7 +11422,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C456" t="n">
         <v>102.8814692633022</v>
@@ -11445,7 +11445,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C457" t="n">
         <v>102.8814692633022</v>
@@ -11468,7 +11468,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C458" t="n">
         <v>102.8814692633022</v>
@@ -11491,7 +11491,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C459" t="n">
         <v>102.8814692633022</v>
@@ -11514,7 +11514,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C460" t="n">
         <v>102.8814692633022</v>
@@ -11537,7 +11537,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C461" t="n">
         <v>102.8814692633022</v>
@@ -11560,7 +11560,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C462" t="n">
         <v>102.8814692633022</v>
@@ -11583,7 +11583,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C463" t="n">
         <v>102.8814692633022</v>
@@ -11606,7 +11606,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C464" t="n">
         <v>102.8814692633022</v>
@@ -11629,7 +11629,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C465" t="n">
         <v>102.8814692633022</v>
@@ -11652,7 +11652,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C466" t="n">
         <v>102.8814692633022</v>
@@ -11675,7 +11675,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C467" t="n">
         <v>102.8814692633022</v>
@@ -11698,7 +11698,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C468" t="n">
         <v>102.8814692633022</v>
@@ -11721,7 +11721,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C469" t="n">
         <v>102.8814692633022</v>
@@ -11744,7 +11744,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C470" t="n">
         <v>102.8814692633022</v>
@@ -11767,7 +11767,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C471" t="n">
         <v>102.8814692633022</v>
@@ -11790,7 +11790,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C472" t="n">
         <v>102.8814692633022</v>
@@ -11813,7 +11813,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C473" t="n">
         <v>102.8814692633022</v>
@@ -11836,7 +11836,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C474" t="n">
         <v>102.8814692633022</v>
@@ -11859,7 +11859,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C475" t="n">
         <v>102.8814692633022</v>
@@ -11882,7 +11882,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C476" t="n">
         <v>102.8814692633022</v>
@@ -11905,7 +11905,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C477" t="n">
         <v>102.8814692633022</v>
@@ -11928,7 +11928,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C478" t="n">
         <v>102.8814692633022</v>
@@ -11951,7 +11951,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C479" t="n">
         <v>102.8814692633022</v>
@@ -11974,7 +11974,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C480" t="n">
         <v>102.8814692633022</v>
@@ -11997,7 +11997,7 @@
         <v>479</v>
       </c>
       <c r="B481" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C481" t="n">
         <v>102.8814692633022</v>
@@ -12020,7 +12020,7 @@
         <v>480</v>
       </c>
       <c r="B482" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C482" t="n">
         <v>102.8814692633022</v>
@@ -12043,7 +12043,7 @@
         <v>481</v>
       </c>
       <c r="B483" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C483" t="n">
         <v>102.8814692633022</v>
@@ -12066,7 +12066,7 @@
         <v>482</v>
       </c>
       <c r="B484" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C484" t="n">
         <v>102.8814692633022</v>
@@ -12089,7 +12089,7 @@
         <v>483</v>
       </c>
       <c r="B485" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C485" t="n">
         <v>102.8814692633022</v>
@@ -12112,7 +12112,7 @@
         <v>484</v>
       </c>
       <c r="B486" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C486" t="n">
         <v>102.8814692633022</v>
@@ -12135,7 +12135,7 @@
         <v>485</v>
       </c>
       <c r="B487" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C487" t="n">
         <v>102.8814692633022</v>
@@ -12158,7 +12158,7 @@
         <v>486</v>
       </c>
       <c r="B488" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C488" t="n">
         <v>102.8814692633022</v>
@@ -12181,7 +12181,7 @@
         <v>487</v>
       </c>
       <c r="B489" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C489" t="n">
         <v>102.8814692633022</v>
@@ -12204,7 +12204,7 @@
         <v>488</v>
       </c>
       <c r="B490" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C490" t="n">
         <v>102.8814692633022</v>
@@ -12227,7 +12227,7 @@
         <v>489</v>
       </c>
       <c r="B491" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C491" t="n">
         <v>102.8814692633022</v>
@@ -12250,7 +12250,7 @@
         <v>490</v>
       </c>
       <c r="B492" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C492" t="n">
         <v>102.8814692633022</v>
@@ -12273,7 +12273,7 @@
         <v>491</v>
       </c>
       <c r="B493" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C493" t="n">
         <v>102.8814692633022</v>
@@ -12296,7 +12296,7 @@
         <v>492</v>
       </c>
       <c r="B494" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C494" t="n">
         <v>102.8814692633022</v>
@@ -12319,7 +12319,7 @@
         <v>493</v>
       </c>
       <c r="B495" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C495" t="n">
         <v>102.8814692633022</v>
@@ -12342,7 +12342,7 @@
         <v>494</v>
       </c>
       <c r="B496" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C496" t="n">
         <v>102.8814692633022</v>
@@ -17172,7 +17172,7 @@
         <v>704</v>
       </c>
       <c r="B706" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C706" t="n">
         <v>103.1693583347785</v>
@@ -17195,7 +17195,7 @@
         <v>705</v>
       </c>
       <c r="B707" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C707" t="n">
         <v>103.1693583347785</v>
@@ -17218,7 +17218,7 @@
         <v>706</v>
       </c>
       <c r="B708" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C708" t="n">
         <v>103.1693583347785</v>
@@ -17241,7 +17241,7 @@
         <v>707</v>
       </c>
       <c r="B709" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C709" t="n">
         <v>103.1693583347785</v>
@@ -17264,7 +17264,7 @@
         <v>708</v>
       </c>
       <c r="B710" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C710" t="n">
         <v>103.1693583347785</v>
@@ -17287,7 +17287,7 @@
         <v>709</v>
       </c>
       <c r="B711" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C711" t="n">
         <v>103.1693583347785</v>
@@ -17310,7 +17310,7 @@
         <v>710</v>
       </c>
       <c r="B712" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C712" t="n">
         <v>103.1693583347785</v>
@@ -17333,7 +17333,7 @@
         <v>711</v>
       </c>
       <c r="B713" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C713" t="n">
         <v>103.1693583347785</v>
@@ -17356,7 +17356,7 @@
         <v>712</v>
       </c>
       <c r="B714" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C714" t="n">
         <v>103.1693583347785</v>
@@ -17379,7 +17379,7 @@
         <v>713</v>
       </c>
       <c r="B715" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C715" t="n">
         <v>103.1693583347785</v>
@@ -17402,7 +17402,7 @@
         <v>714</v>
       </c>
       <c r="B716" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C716" t="n">
         <v>103.1693583347785</v>
@@ -17425,7 +17425,7 @@
         <v>715</v>
       </c>
       <c r="B717" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C717" t="n">
         <v>103.1693583347785</v>
@@ -17448,7 +17448,7 @@
         <v>716</v>
       </c>
       <c r="B718" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C718" t="n">
         <v>103.1693583347785</v>
@@ -17471,7 +17471,7 @@
         <v>717</v>
       </c>
       <c r="B719" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C719" t="n">
         <v>103.1693583347785</v>
@@ -17494,7 +17494,7 @@
         <v>718</v>
       </c>
       <c r="B720" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C720" t="n">
         <v>103.1693583347785</v>
@@ -17517,7 +17517,7 @@
         <v>719</v>
       </c>
       <c r="B721" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C721" t="n">
         <v>103.1693583347785</v>
@@ -17540,7 +17540,7 @@
         <v>720</v>
       </c>
       <c r="B722" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C722" t="n">
         <v>103.1693583347785</v>
@@ -17563,7 +17563,7 @@
         <v>721</v>
       </c>
       <c r="B723" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C723" t="n">
         <v>103.1693583347785</v>
@@ -17586,7 +17586,7 @@
         <v>722</v>
       </c>
       <c r="B724" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C724" t="n">
         <v>103.1693583347785</v>
@@ -17609,7 +17609,7 @@
         <v>723</v>
       </c>
       <c r="B725" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C725" t="n">
         <v>103.1693583347785</v>
@@ -17632,7 +17632,7 @@
         <v>724</v>
       </c>
       <c r="B726" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C726" t="n">
         <v>103.1693583347785</v>
@@ -17655,7 +17655,7 @@
         <v>725</v>
       </c>
       <c r="B727" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C727" t="n">
         <v>103.1693583347785</v>
@@ -17678,7 +17678,7 @@
         <v>726</v>
       </c>
       <c r="B728" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C728" t="n">
         <v>103.1693583347785</v>
@@ -17701,7 +17701,7 @@
         <v>727</v>
       </c>
       <c r="B729" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C729" t="n">
         <v>103.1693583347785</v>
@@ -17724,7 +17724,7 @@
         <v>728</v>
       </c>
       <c r="B730" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C730" t="n">
         <v>103.1693583347785</v>
@@ -17747,7 +17747,7 @@
         <v>729</v>
       </c>
       <c r="B731" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C731" t="n">
         <v>103.1693583347785</v>
@@ -17770,7 +17770,7 @@
         <v>730</v>
       </c>
       <c r="B732" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C732" t="n">
         <v>103.1693583347785</v>
@@ -17793,7 +17793,7 @@
         <v>731</v>
       </c>
       <c r="B733" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C733" t="n">
         <v>103.1693583347785</v>
@@ -17816,7 +17816,7 @@
         <v>732</v>
       </c>
       <c r="B734" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C734" t="n">
         <v>103.1693583347785</v>
@@ -17839,7 +17839,7 @@
         <v>733</v>
       </c>
       <c r="B735" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C735" t="n">
         <v>103.1693583347785</v>
@@ -17862,7 +17862,7 @@
         <v>734</v>
       </c>
       <c r="B736" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C736" t="n">
         <v>103.1693583347785</v>
@@ -17885,7 +17885,7 @@
         <v>735</v>
       </c>
       <c r="B737" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C737" t="n">
         <v>103.1693583347785</v>
@@ -17908,7 +17908,7 @@
         <v>736</v>
       </c>
       <c r="B738" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C738" t="n">
         <v>103.1693583347785</v>
@@ -17931,7 +17931,7 @@
         <v>737</v>
       </c>
       <c r="B739" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C739" t="n">
         <v>103.1693583347785</v>
@@ -17954,7 +17954,7 @@
         <v>738</v>
       </c>
       <c r="B740" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C740" t="n">
         <v>103.1693583347785</v>
@@ -17977,7 +17977,7 @@
         <v>739</v>
       </c>
       <c r="B741" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C741" t="n">
         <v>103.1693583347785</v>
@@ -18000,7 +18000,7 @@
         <v>740</v>
       </c>
       <c r="B742" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C742" t="n">
         <v>103.1693583347785</v>
@@ -18023,7 +18023,7 @@
         <v>741</v>
       </c>
       <c r="B743" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C743" t="n">
         <v>103.1693583347785</v>
@@ -18046,7 +18046,7 @@
         <v>742</v>
       </c>
       <c r="B744" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C744" t="n">
         <v>103.1693583347785</v>
@@ -18069,7 +18069,7 @@
         <v>743</v>
       </c>
       <c r="B745" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C745" t="n">
         <v>103.1693583347785</v>
@@ -18092,7 +18092,7 @@
         <v>744</v>
       </c>
       <c r="B746" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C746" t="n">
         <v>103.1693583347785</v>
@@ -18115,7 +18115,7 @@
         <v>745</v>
       </c>
       <c r="B747" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C747" t="n">
         <v>103.1693583347785</v>
@@ -18138,7 +18138,7 @@
         <v>746</v>
       </c>
       <c r="B748" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C748" t="n">
         <v>103.1693583347785</v>
@@ -18161,7 +18161,7 @@
         <v>747</v>
       </c>
       <c r="B749" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C749" t="n">
         <v>103.1693583347785</v>
@@ -18184,7 +18184,7 @@
         <v>748</v>
       </c>
       <c r="B750" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C750" t="n">
         <v>103.1693583347785</v>
@@ -18207,7 +18207,7 @@
         <v>749</v>
       </c>
       <c r="B751" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C751" t="n">
         <v>103.1693583347785</v>
@@ -18230,7 +18230,7 @@
         <v>750</v>
       </c>
       <c r="B752" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C752" t="n">
         <v>103.1693583347785</v>
@@ -18253,7 +18253,7 @@
         <v>751</v>
       </c>
       <c r="B753" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C753" t="n">
         <v>103.1693583347785</v>
@@ -18276,7 +18276,7 @@
         <v>752</v>
       </c>
       <c r="B754" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C754" t="n">
         <v>103.1693583347785</v>
@@ -18299,7 +18299,7 @@
         <v>753</v>
       </c>
       <c r="B755" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C755" t="n">
         <v>103.1693583347785</v>
@@ -18322,7 +18322,7 @@
         <v>754</v>
       </c>
       <c r="B756" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C756" t="n">
         <v>103.1693583347785</v>
@@ -18345,7 +18345,7 @@
         <v>755</v>
       </c>
       <c r="B757" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C757" t="n">
         <v>103.1693583347785</v>
@@ -18368,7 +18368,7 @@
         <v>756</v>
       </c>
       <c r="B758" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C758" t="n">
         <v>103.1693583347785</v>
@@ -18391,7 +18391,7 @@
         <v>757</v>
       </c>
       <c r="B759" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C759" t="n">
         <v>103.1693583347785</v>
@@ -18414,7 +18414,7 @@
         <v>758</v>
       </c>
       <c r="B760" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C760" t="n">
         <v>103.1693583347785</v>
@@ -18437,7 +18437,7 @@
         <v>759</v>
       </c>
       <c r="B761" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C761" t="n">
         <v>103.1693583347785</v>
@@ -18460,7 +18460,7 @@
         <v>760</v>
       </c>
       <c r="B762" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C762" t="n">
         <v>103.1693583347785</v>
@@ -18483,7 +18483,7 @@
         <v>761</v>
       </c>
       <c r="B763" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C763" t="n">
         <v>103.1693583347785</v>
@@ -18506,7 +18506,7 @@
         <v>762</v>
       </c>
       <c r="B764" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C764" t="n">
         <v>103.1693583347785</v>
@@ -18529,7 +18529,7 @@
         <v>763</v>
       </c>
       <c r="B765" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C765" t="n">
         <v>103.1693583347785</v>
@@ -18552,7 +18552,7 @@
         <v>764</v>
       </c>
       <c r="B766" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C766" t="n">
         <v>103.1693583347785</v>
@@ -18575,7 +18575,7 @@
         <v>765</v>
       </c>
       <c r="B767" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C767" t="n">
         <v>103.1693583347785</v>
@@ -18598,7 +18598,7 @@
         <v>766</v>
       </c>
       <c r="B768" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C768" t="n">
         <v>103.1693583347785</v>
@@ -18621,7 +18621,7 @@
         <v>767</v>
       </c>
       <c r="B769" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C769" t="n">
         <v>103.1693583347785</v>
@@ -18644,7 +18644,7 @@
         <v>768</v>
       </c>
       <c r="B770" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C770" t="n">
         <v>103.1693583347785</v>
@@ -18667,7 +18667,7 @@
         <v>769</v>
       </c>
       <c r="B771" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C771" t="n">
         <v>103.1693583347785</v>
@@ -18690,7 +18690,7 @@
         <v>770</v>
       </c>
       <c r="B772" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C772" t="n">
         <v>103.1693583347785</v>
@@ -18713,7 +18713,7 @@
         <v>771</v>
       </c>
       <c r="B773" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C773" t="n">
         <v>103.1693583347785</v>
@@ -18736,7 +18736,7 @@
         <v>772</v>
       </c>
       <c r="B774" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C774" t="n">
         <v>103.1693583347785</v>
@@ -18759,7 +18759,7 @@
         <v>773</v>
       </c>
       <c r="B775" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C775" t="n">
         <v>103.1693583347785</v>
@@ -18782,7 +18782,7 @@
         <v>774</v>
       </c>
       <c r="B776" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C776" t="n">
         <v>103.1693583347785</v>
@@ -18805,7 +18805,7 @@
         <v>775</v>
       </c>
       <c r="B777" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C777" t="n">
         <v>103.1693583347785</v>
@@ -18828,7 +18828,7 @@
         <v>776</v>
       </c>
       <c r="B778" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C778" t="n">
         <v>103.1693583347785</v>
@@ -18851,7 +18851,7 @@
         <v>777</v>
       </c>
       <c r="B779" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C779" t="n">
         <v>103.1693583347785</v>
@@ -18874,7 +18874,7 @@
         <v>778</v>
       </c>
       <c r="B780" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C780" t="n">
         <v>103.1693583347785</v>
@@ -18897,7 +18897,7 @@
         <v>779</v>
       </c>
       <c r="B781" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C781" t="n">
         <v>103.1693583347785</v>
@@ -18920,7 +18920,7 @@
         <v>780</v>
       </c>
       <c r="B782" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C782" t="n">
         <v>103.1693583347785</v>
@@ -18943,7 +18943,7 @@
         <v>781</v>
       </c>
       <c r="B783" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C783" t="n">
         <v>103.1693583347785</v>
@@ -18966,7 +18966,7 @@
         <v>782</v>
       </c>
       <c r="B784" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C784" t="n">
         <v>103.1693583347785</v>
@@ -18989,7 +18989,7 @@
         <v>783</v>
       </c>
       <c r="B785" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C785" t="n">
         <v>103.1693583347785</v>
@@ -19012,7 +19012,7 @@
         <v>784</v>
       </c>
       <c r="B786" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C786" t="n">
         <v>103.1693583347785</v>
@@ -19035,7 +19035,7 @@
         <v>785</v>
       </c>
       <c r="B787" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C787" t="n">
         <v>103.1693583347785</v>
@@ -19058,7 +19058,7 @@
         <v>786</v>
       </c>
       <c r="B788" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C788" t="n">
         <v>103.1693583347785</v>
@@ -19081,7 +19081,7 @@
         <v>787</v>
       </c>
       <c r="B789" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C789" t="n">
         <v>103.1693583347785</v>
@@ -19104,7 +19104,7 @@
         <v>788</v>
       </c>
       <c r="B790" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C790" t="n">
         <v>103.1693583347785</v>
@@ -19127,7 +19127,7 @@
         <v>789</v>
       </c>
       <c r="B791" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C791" t="n">
         <v>103.1693583347785</v>
@@ -19150,7 +19150,7 @@
         <v>790</v>
       </c>
       <c r="B792" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C792" t="n">
         <v>103.1693583347785</v>
@@ -19173,7 +19173,7 @@
         <v>791</v>
       </c>
       <c r="B793" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C793" t="n">
         <v>103.1693583347785</v>
@@ -19196,7 +19196,7 @@
         <v>792</v>
       </c>
       <c r="B794" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C794" t="n">
         <v>103.1693583347785</v>
@@ -19219,7 +19219,7 @@
         <v>793</v>
       </c>
       <c r="B795" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C795" t="n">
         <v>103.1693583347785</v>
@@ -19242,7 +19242,7 @@
         <v>794</v>
       </c>
       <c r="B796" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C796" t="n">
         <v>103.1693583347785</v>
@@ -19265,7 +19265,7 @@
         <v>795</v>
       </c>
       <c r="B797" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C797" t="n">
         <v>103.1693583347785</v>
@@ -19288,7 +19288,7 @@
         <v>796</v>
       </c>
       <c r="B798" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C798" t="n">
         <v>103.1693583347785</v>
@@ -19311,7 +19311,7 @@
         <v>797</v>
       </c>
       <c r="B799" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C799" t="n">
         <v>103.1693583347785</v>
@@ -19334,7 +19334,7 @@
         <v>798</v>
       </c>
       <c r="B800" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C800" t="n">
         <v>103.1693583347785</v>
@@ -19357,7 +19357,7 @@
         <v>799</v>
       </c>
       <c r="B801" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C801" t="n">
         <v>103.1693583347785</v>
@@ -19380,7 +19380,7 @@
         <v>800</v>
       </c>
       <c r="B802" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C802" t="n">
         <v>103.1693583347785</v>
@@ -19403,7 +19403,7 @@
         <v>801</v>
       </c>
       <c r="B803" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C803" t="n">
         <v>103.1693583347785</v>
@@ -19426,7 +19426,7 @@
         <v>802</v>
       </c>
       <c r="B804" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C804" t="n">
         <v>103.1693583347785</v>
@@ -19449,7 +19449,7 @@
         <v>803</v>
       </c>
       <c r="B805" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C805" t="n">
         <v>103.1693583347785</v>
@@ -19472,7 +19472,7 @@
         <v>804</v>
       </c>
       <c r="B806" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C806" t="n">
         <v>103.1693583347785</v>
@@ -19495,7 +19495,7 @@
         <v>805</v>
       </c>
       <c r="B807" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C807" t="n">
         <v>103.1693583347785</v>
@@ -19518,7 +19518,7 @@
         <v>806</v>
       </c>
       <c r="B808" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C808" t="n">
         <v>103.1693583347785</v>
@@ -19541,7 +19541,7 @@
         <v>807</v>
       </c>
       <c r="B809" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C809" t="n">
         <v>103.1693583347785</v>
@@ -19564,7 +19564,7 @@
         <v>808</v>
       </c>
       <c r="B810" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C810" t="n">
         <v>103.1693583347785</v>
@@ -19587,7 +19587,7 @@
         <v>809</v>
       </c>
       <c r="B811" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C811" t="n">
         <v>103.1693583347785</v>
@@ -19610,7 +19610,7 @@
         <v>810</v>
       </c>
       <c r="B812" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C812" t="n">
         <v>103.1693583347785</v>
@@ -19633,7 +19633,7 @@
         <v>811</v>
       </c>
       <c r="B813" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C813" t="n">
         <v>103.1693583347785</v>
@@ -19656,7 +19656,7 @@
         <v>812</v>
       </c>
       <c r="B814" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C814" t="n">
         <v>103.1693583347785</v>
@@ -19679,7 +19679,7 @@
         <v>813</v>
       </c>
       <c r="B815" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C815" t="n">
         <v>103.1693583347785</v>
@@ -19702,7 +19702,7 @@
         <v>814</v>
       </c>
       <c r="B816" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C816" t="n">
         <v>103.1693583347785</v>
@@ -19725,7 +19725,7 @@
         <v>815</v>
       </c>
       <c r="B817" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C817" t="n">
         <v>103.1693583347785</v>
@@ -19748,7 +19748,7 @@
         <v>816</v>
       </c>
       <c r="B818" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C818" t="n">
         <v>103.1693583347785</v>
@@ -19771,7 +19771,7 @@
         <v>817</v>
       </c>
       <c r="B819" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C819" t="n">
         <v>103.1693583347785</v>
@@ -19794,7 +19794,7 @@
         <v>818</v>
       </c>
       <c r="B820" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C820" t="n">
         <v>103.1693583347785</v>
@@ -19817,7 +19817,7 @@
         <v>819</v>
       </c>
       <c r="B821" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C821" t="n">
         <v>103.1693583347785</v>
@@ -19840,7 +19840,7 @@
         <v>820</v>
       </c>
       <c r="B822" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C822" t="n">
         <v>103.1693583347785</v>
@@ -19863,7 +19863,7 @@
         <v>821</v>
       </c>
       <c r="B823" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C823" t="n">
         <v>103.1693583347785</v>
@@ -19886,7 +19886,7 @@
         <v>822</v>
       </c>
       <c r="B824" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C824" t="n">
         <v>103.1693583347785</v>
@@ -19909,7 +19909,7 @@
         <v>823</v>
       </c>
       <c r="B825" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C825" t="n">
         <v>103.1693583347785</v>
@@ -19932,7 +19932,7 @@
         <v>824</v>
       </c>
       <c r="B826" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C826" t="n">
         <v>103.1693583347785</v>
@@ -19955,7 +19955,7 @@
         <v>825</v>
       </c>
       <c r="B827" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C827" t="n">
         <v>103.1693583347785</v>
@@ -19978,7 +19978,7 @@
         <v>826</v>
       </c>
       <c r="B828" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C828" t="n">
         <v>103.1693583347785</v>
@@ -20001,7 +20001,7 @@
         <v>827</v>
       </c>
       <c r="B829" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C829" t="n">
         <v>103.1693583347785</v>
@@ -20024,7 +20024,7 @@
         <v>828</v>
       </c>
       <c r="B830" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C830" t="n">
         <v>103.1693583347785</v>
@@ -20047,7 +20047,7 @@
         <v>829</v>
       </c>
       <c r="B831" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C831" t="n">
         <v>103.1693583347785</v>
@@ -20070,7 +20070,7 @@
         <v>830</v>
       </c>
       <c r="B832" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C832" t="n">
         <v>103.1693583347785</v>
@@ -20093,7 +20093,7 @@
         <v>831</v>
       </c>
       <c r="B833" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C833" t="n">
         <v>103.1693583347785</v>
@@ -20116,7 +20116,7 @@
         <v>832</v>
       </c>
       <c r="B834" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C834" t="n">
         <v>103.1693583347785</v>
@@ -20139,7 +20139,7 @@
         <v>833</v>
       </c>
       <c r="B835" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C835" t="n">
         <v>103.1693583347785</v>
@@ -20162,7 +20162,7 @@
         <v>834</v>
       </c>
       <c r="B836" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C836" t="n">
         <v>103.1693583347785</v>
@@ -20185,7 +20185,7 @@
         <v>835</v>
       </c>
       <c r="B837" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C837" t="n">
         <v>103.1693583347785</v>
@@ -20208,7 +20208,7 @@
         <v>836</v>
       </c>
       <c r="B838" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C838" t="n">
         <v>103.1693583347785</v>
@@ -20231,7 +20231,7 @@
         <v>837</v>
       </c>
       <c r="B839" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C839" t="n">
         <v>103.1693583347785</v>
@@ -20254,7 +20254,7 @@
         <v>838</v>
       </c>
       <c r="B840" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C840" t="n">
         <v>103.1693583347785</v>
@@ -20277,7 +20277,7 @@
         <v>839</v>
       </c>
       <c r="B841" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C841" t="n">
         <v>103.1693583347785</v>
@@ -20300,7 +20300,7 @@
         <v>840</v>
       </c>
       <c r="B842" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C842" t="n">
         <v>103.1693583347785</v>
@@ -20323,7 +20323,7 @@
         <v>841</v>
       </c>
       <c r="B843" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C843" t="n">
         <v>103.1693583347785</v>
@@ -20346,7 +20346,7 @@
         <v>842</v>
       </c>
       <c r="B844" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C844" t="n">
         <v>103.1693583347785</v>
@@ -20369,7 +20369,7 @@
         <v>843</v>
       </c>
       <c r="B845" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C845" t="n">
         <v>103.1693583347785</v>
@@ -20392,7 +20392,7 @@
         <v>844</v>
       </c>
       <c r="B846" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C846" t="n">
         <v>103.1693583347785</v>
@@ -20415,7 +20415,7 @@
         <v>845</v>
       </c>
       <c r="B847" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C847" t="n">
         <v>103.1693583347785</v>
@@ -20438,7 +20438,7 @@
         <v>846</v>
       </c>
       <c r="B848" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C848" t="n">
         <v>103.1693583347785</v>
@@ -20461,7 +20461,7 @@
         <v>847</v>
       </c>
       <c r="B849" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C849" t="n">
         <v>103.1693583347785</v>
@@ -20484,7 +20484,7 @@
         <v>848</v>
       </c>
       <c r="B850" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C850" t="n">
         <v>103.1693583347785</v>
@@ -20507,7 +20507,7 @@
         <v>849</v>
       </c>
       <c r="B851" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C851" t="n">
         <v>103.1693583347785</v>
@@ -20530,7 +20530,7 @@
         <v>850</v>
       </c>
       <c r="B852" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C852" t="n">
         <v>103.1693583347785</v>
@@ -20553,7 +20553,7 @@
         <v>851</v>
       </c>
       <c r="B853" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C853" t="n">
         <v>103.1693583347785</v>
@@ -20576,7 +20576,7 @@
         <v>852</v>
       </c>
       <c r="B854" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C854" t="n">
         <v>103.1693583347785</v>
@@ -20599,7 +20599,7 @@
         <v>853</v>
       </c>
       <c r="B855" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C855" t="n">
         <v>103.1693583347785</v>
@@ -20622,7 +20622,7 @@
         <v>854</v>
       </c>
       <c r="B856" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C856" t="n">
         <v>103.1693583347785</v>
@@ -20645,7 +20645,7 @@
         <v>855</v>
       </c>
       <c r="B857" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C857" t="n">
         <v>103.1693583347785</v>
@@ -20668,7 +20668,7 @@
         <v>856</v>
       </c>
       <c r="B858" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C858" t="n">
         <v>103.1693583347785</v>
@@ -20691,7 +20691,7 @@
         <v>857</v>
       </c>
       <c r="B859" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C859" t="n">
         <v>103.1693583347785</v>
@@ -20714,7 +20714,7 @@
         <v>858</v>
       </c>
       <c r="B860" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C860" t="n">
         <v>103.1693583347785</v>
@@ -20737,7 +20737,7 @@
         <v>859</v>
       </c>
       <c r="B861" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C861" t="n">
         <v>103.1693583347785</v>
@@ -20760,7 +20760,7 @@
         <v>860</v>
       </c>
       <c r="B862" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C862" t="n">
         <v>103.1693583347785</v>
@@ -20783,7 +20783,7 @@
         <v>861</v>
       </c>
       <c r="B863" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C863" t="n">
         <v>103.1693583347785</v>
@@ -20806,7 +20806,7 @@
         <v>862</v>
       </c>
       <c r="B864" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C864" t="n">
         <v>103.1693583347785</v>
@@ -20829,7 +20829,7 @@
         <v>863</v>
       </c>
       <c r="B865" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C865" t="n">
         <v>103.1693583347785</v>
@@ -20852,7 +20852,7 @@
         <v>864</v>
       </c>
       <c r="B866" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C866" t="n">
         <v>103.1693583347785</v>
@@ -20875,7 +20875,7 @@
         <v>865</v>
       </c>
       <c r="B867" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C867" t="n">
         <v>103.1693583347785</v>
@@ -20898,7 +20898,7 @@
         <v>866</v>
       </c>
       <c r="B868" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C868" t="n">
         <v>103.1693583347785</v>
@@ -20921,7 +20921,7 @@
         <v>867</v>
       </c>
       <c r="B869" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C869" t="n">
         <v>103.1693583347785</v>
@@ -20944,7 +20944,7 @@
         <v>868</v>
       </c>
       <c r="B870" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C870" t="n">
         <v>103.1693583347785</v>
@@ -20967,7 +20967,7 @@
         <v>869</v>
       </c>
       <c r="B871" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C871" t="n">
         <v>103.1693583347785</v>
@@ -20990,7 +20990,7 @@
         <v>870</v>
       </c>
       <c r="B872" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C872" t="n">
         <v>103.1693583347785</v>
@@ -21013,7 +21013,7 @@
         <v>871</v>
       </c>
       <c r="B873" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C873" t="n">
         <v>103.1693583347785</v>
@@ -21036,7 +21036,7 @@
         <v>872</v>
       </c>
       <c r="B874" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C874" t="n">
         <v>103.1693583347785</v>
@@ -21059,7 +21059,7 @@
         <v>873</v>
       </c>
       <c r="B875" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C875" t="n">
         <v>103.1693583347785</v>
@@ -21082,7 +21082,7 @@
         <v>874</v>
       </c>
       <c r="B876" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C876" t="n">
         <v>103.1693583347785</v>
@@ -21105,7 +21105,7 @@
         <v>875</v>
       </c>
       <c r="B877" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C877" t="n">
         <v>103.1693583347785</v>
@@ -21128,7 +21128,7 @@
         <v>876</v>
       </c>
       <c r="B878" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C878" t="n">
         <v>103.1693583347785</v>
@@ -21151,7 +21151,7 @@
         <v>877</v>
       </c>
       <c r="B879" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C879" t="n">
         <v>103.1693583347785</v>
@@ -21174,7 +21174,7 @@
         <v>878</v>
       </c>
       <c r="B880" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C880" t="n">
         <v>103.1693583347785</v>
@@ -21197,7 +21197,7 @@
         <v>879</v>
       </c>
       <c r="B881" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C881" t="n">
         <v>103.1693583347785</v>
@@ -21220,7 +21220,7 @@
         <v>880</v>
       </c>
       <c r="B882" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C882" t="n">
         <v>103.1693583347785</v>
@@ -21243,7 +21243,7 @@
         <v>881</v>
       </c>
       <c r="B883" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C883" t="n">
         <v>103.1693583347785</v>
@@ -21266,7 +21266,7 @@
         <v>882</v>
       </c>
       <c r="B884" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C884" t="n">
         <v>103.1693583347785</v>
@@ -21289,7 +21289,7 @@
         <v>883</v>
       </c>
       <c r="B885" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C885" t="n">
         <v>103.1693583347785</v>
@@ -26855,7 +26855,7 @@
         <v>1125</v>
       </c>
       <c r="B1127" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1127" t="n">
         <v>0</v>
@@ -26878,7 +26878,7 @@
         <v>1126</v>
       </c>
       <c r="B1128" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1128" t="n">
         <v>0</v>
@@ -26901,7 +26901,7 @@
         <v>1127</v>
       </c>
       <c r="B1129" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1129" t="n">
         <v>0</v>
@@ -26924,7 +26924,7 @@
         <v>1128</v>
       </c>
       <c r="B1130" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1130" t="n">
         <v>0</v>
@@ -26947,7 +26947,7 @@
         <v>1129</v>
       </c>
       <c r="B1131" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1131" t="n">
         <v>0</v>
@@ -26970,7 +26970,7 @@
         <v>1130</v>
       </c>
       <c r="B1132" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1132" t="n">
         <v>0</v>
@@ -26993,7 +26993,7 @@
         <v>1131</v>
       </c>
       <c r="B1133" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1133" t="n">
         <v>0</v>
@@ -27016,7 +27016,7 @@
         <v>1132</v>
       </c>
       <c r="B1134" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1134" t="n">
         <v>0</v>
@@ -27039,7 +27039,7 @@
         <v>1133</v>
       </c>
       <c r="B1135" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1135" t="n">
         <v>0</v>
@@ -27062,7 +27062,7 @@
         <v>1134</v>
       </c>
       <c r="B1136" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1136" t="n">
         <v>0</v>
@@ -27085,7 +27085,7 @@
         <v>1135</v>
       </c>
       <c r="B1137" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1137" t="n">
         <v>0</v>
@@ -27108,7 +27108,7 @@
         <v>1136</v>
       </c>
       <c r="B1138" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1138" t="n">
         <v>0</v>
@@ -27131,7 +27131,7 @@
         <v>1137</v>
       </c>
       <c r="B1139" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1139" t="n">
         <v>0</v>
@@ -27154,7 +27154,7 @@
         <v>1138</v>
       </c>
       <c r="B1140" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1140" t="n">
         <v>0</v>
@@ -27177,7 +27177,7 @@
         <v>1139</v>
       </c>
       <c r="B1141" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1141" t="n">
         <v>0</v>
@@ -27200,7 +27200,7 @@
         <v>1140</v>
       </c>
       <c r="B1142" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1142" t="n">
         <v>0</v>
@@ -27223,7 +27223,7 @@
         <v>1141</v>
       </c>
       <c r="B1143" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1143" t="n">
         <v>0</v>
@@ -27246,7 +27246,7 @@
         <v>1142</v>
       </c>
       <c r="B1144" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1144" t="n">
         <v>0</v>
@@ -27269,7 +27269,7 @@
         <v>1143</v>
       </c>
       <c r="B1145" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1145" t="n">
         <v>0</v>
@@ -27292,7 +27292,7 @@
         <v>1144</v>
       </c>
       <c r="B1146" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1146" t="n">
         <v>0</v>
@@ -27315,7 +27315,7 @@
         <v>1145</v>
       </c>
       <c r="B1147" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1147" t="n">
         <v>0</v>
@@ -27338,7 +27338,7 @@
         <v>1146</v>
       </c>
       <c r="B1148" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1148" t="n">
         <v>0</v>
@@ -27361,7 +27361,7 @@
         <v>1147</v>
       </c>
       <c r="B1149" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1149" t="n">
         <v>0</v>
@@ -27384,7 +27384,7 @@
         <v>1148</v>
       </c>
       <c r="B1150" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1150" t="n">
         <v>0</v>
@@ -27407,7 +27407,7 @@
         <v>1149</v>
       </c>
       <c r="B1151" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1151" t="n">
         <v>0</v>
@@ -27430,7 +27430,7 @@
         <v>1150</v>
       </c>
       <c r="B1152" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1152" t="n">
         <v>0</v>
@@ -27453,7 +27453,7 @@
         <v>1151</v>
       </c>
       <c r="B1153" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1153" t="n">
         <v>0</v>
@@ -27476,7 +27476,7 @@
         <v>1152</v>
       </c>
       <c r="B1154" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1154" t="n">
         <v>0</v>
@@ -27499,7 +27499,7 @@
         <v>1153</v>
       </c>
       <c r="B1155" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1155" t="n">
         <v>0</v>
@@ -27522,7 +27522,7 @@
         <v>1154</v>
       </c>
       <c r="B1156" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1156" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
         <v>1155</v>
       </c>
       <c r="B1157" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1157" t="n">
         <v>0</v>
@@ -27568,7 +27568,7 @@
         <v>1156</v>
       </c>
       <c r="B1158" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1158" t="n">
         <v>0</v>
@@ -27591,7 +27591,7 @@
         <v>1157</v>
       </c>
       <c r="B1159" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1159" t="n">
         <v>0</v>
@@ -27614,7 +27614,7 @@
         <v>1158</v>
       </c>
       <c r="B1160" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1160" t="n">
         <v>0</v>
@@ -27637,7 +27637,7 @@
         <v>1159</v>
       </c>
       <c r="B1161" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1161" t="n">
         <v>0</v>
@@ -27660,7 +27660,7 @@
         <v>1160</v>
       </c>
       <c r="B1162" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1162" t="n">
         <v>0</v>
@@ -27683,7 +27683,7 @@
         <v>1161</v>
       </c>
       <c r="B1163" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1163" t="n">
         <v>0</v>
@@ -27706,7 +27706,7 @@
         <v>1162</v>
       </c>
       <c r="B1164" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1164" t="n">
         <v>0</v>
@@ -27729,7 +27729,7 @@
         <v>1163</v>
       </c>
       <c r="B1165" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1165" t="n">
         <v>0</v>
@@ -27752,7 +27752,7 @@
         <v>1164</v>
       </c>
       <c r="B1166" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1166" t="n">
         <v>0</v>
@@ -27775,7 +27775,7 @@
         <v>1165</v>
       </c>
       <c r="B1167" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1167" t="n">
         <v>0</v>
@@ -27798,7 +27798,7 @@
         <v>1166</v>
       </c>
       <c r="B1168" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1168" t="n">
         <v>0</v>
@@ -27821,7 +27821,7 @@
         <v>1167</v>
       </c>
       <c r="B1169" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1169" t="n">
         <v>0</v>
@@ -27844,7 +27844,7 @@
         <v>1168</v>
       </c>
       <c r="B1170" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1170" t="n">
         <v>0</v>
@@ -27867,7 +27867,7 @@
         <v>1169</v>
       </c>
       <c r="B1171" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1171" t="n">
         <v>0</v>
@@ -27890,7 +27890,7 @@
         <v>1170</v>
       </c>
       <c r="B1172" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1172" t="n">
         <v>0</v>
@@ -27913,7 +27913,7 @@
         <v>1171</v>
       </c>
       <c r="B1173" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1173" t="n">
         <v>0</v>
@@ -27936,7 +27936,7 @@
         <v>1172</v>
       </c>
       <c r="B1174" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1174" t="n">
         <v>0</v>
@@ -27959,7 +27959,7 @@
         <v>1173</v>
       </c>
       <c r="B1175" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1175" t="n">
         <v>0</v>
@@ -27982,7 +27982,7 @@
         <v>1174</v>
       </c>
       <c r="B1176" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1176" t="n">
         <v>0</v>
@@ -28005,7 +28005,7 @@
         <v>1175</v>
       </c>
       <c r="B1177" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1177" t="n">
         <v>0</v>
@@ -28028,7 +28028,7 @@
         <v>1176</v>
       </c>
       <c r="B1178" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1178" t="n">
         <v>0</v>
@@ -28051,7 +28051,7 @@
         <v>1177</v>
       </c>
       <c r="B1179" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1179" t="n">
         <v>0</v>
@@ -28074,7 +28074,7 @@
         <v>1178</v>
       </c>
       <c r="B1180" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1180" t="n">
         <v>0</v>
@@ -28097,7 +28097,7 @@
         <v>1179</v>
       </c>
       <c r="B1181" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1181" t="n">
         <v>0</v>
@@ -28120,7 +28120,7 @@
         <v>1180</v>
       </c>
       <c r="B1182" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1182" t="n">
         <v>0</v>
@@ -28143,7 +28143,7 @@
         <v>1181</v>
       </c>
       <c r="B1183" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1183" t="n">
         <v>0</v>
@@ -28166,7 +28166,7 @@
         <v>1182</v>
       </c>
       <c r="B1184" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1184" t="n">
         <v>0</v>
@@ -28189,7 +28189,7 @@
         <v>1183</v>
       </c>
       <c r="B1185" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1185" t="n">
         <v>0</v>
@@ -28212,7 +28212,7 @@
         <v>1184</v>
       </c>
       <c r="B1186" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1186" t="n">
         <v>0</v>
@@ -28235,7 +28235,7 @@
         <v>1185</v>
       </c>
       <c r="B1187" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1187" t="n">
         <v>0</v>
@@ -28258,7 +28258,7 @@
         <v>1186</v>
       </c>
       <c r="B1188" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1188" t="n">
         <v>0</v>
@@ -28281,7 +28281,7 @@
         <v>1187</v>
       </c>
       <c r="B1189" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1189" t="n">
         <v>0</v>
@@ -28304,7 +28304,7 @@
         <v>1188</v>
       </c>
       <c r="B1190" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1190" t="n">
         <v>0</v>
@@ -28327,7 +28327,7 @@
         <v>1189</v>
       </c>
       <c r="B1191" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1191" t="n">
         <v>0</v>
@@ -28350,7 +28350,7 @@
         <v>1190</v>
       </c>
       <c r="B1192" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1192" t="n">
         <v>0</v>
@@ -28373,7 +28373,7 @@
         <v>1191</v>
       </c>
       <c r="B1193" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1193" t="n">
         <v>0</v>
@@ -28396,7 +28396,7 @@
         <v>1192</v>
       </c>
       <c r="B1194" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1194" t="n">
         <v>0</v>
@@ -28419,7 +28419,7 @@
         <v>1193</v>
       </c>
       <c r="B1195" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1195" t="n">
         <v>0</v>
@@ -28442,7 +28442,7 @@
         <v>1194</v>
       </c>
       <c r="B1196" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1196" t="n">
         <v>0</v>
@@ -28465,7 +28465,7 @@
         <v>1195</v>
       </c>
       <c r="B1197" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1197" t="n">
         <v>0</v>
@@ -28488,7 +28488,7 @@
         <v>1196</v>
       </c>
       <c r="B1198" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1198" t="n">
         <v>0</v>
@@ -28511,7 +28511,7 @@
         <v>1197</v>
       </c>
       <c r="B1199" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1199" t="n">
         <v>0</v>
@@ -28534,7 +28534,7 @@
         <v>1198</v>
       </c>
       <c r="B1200" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1200" t="n">
         <v>0</v>
@@ -28557,7 +28557,7 @@
         <v>1199</v>
       </c>
       <c r="B1201" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1201" t="n">
         <v>0</v>
@@ -28580,7 +28580,7 @@
         <v>1200</v>
       </c>
       <c r="B1202" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1202" t="n">
         <v>0</v>
@@ -28603,7 +28603,7 @@
         <v>1201</v>
       </c>
       <c r="B1203" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1203" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
         <v>1202</v>
       </c>
       <c r="B1204" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1204" t="n">
         <v>0</v>
@@ -28649,7 +28649,7 @@
         <v>1203</v>
       </c>
       <c r="B1205" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1205" t="n">
         <v>0</v>
@@ -28672,7 +28672,7 @@
         <v>1204</v>
       </c>
       <c r="B1206" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1206" t="n">
         <v>0</v>
@@ -28695,7 +28695,7 @@
         <v>1205</v>
       </c>
       <c r="B1207" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1207" t="n">
         <v>0</v>
@@ -28718,7 +28718,7 @@
         <v>1206</v>
       </c>
       <c r="B1208" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1208" t="n">
         <v>0</v>
@@ -28741,7 +28741,7 @@
         <v>1207</v>
       </c>
       <c r="B1209" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1209" t="n">
         <v>0</v>
@@ -28764,7 +28764,7 @@
         <v>1208</v>
       </c>
       <c r="B1210" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1210" t="n">
         <v>0</v>
@@ -28787,7 +28787,7 @@
         <v>1209</v>
       </c>
       <c r="B1211" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1211" t="n">
         <v>0</v>
@@ -28810,7 +28810,7 @@
         <v>1210</v>
       </c>
       <c r="B1212" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1212" t="n">
         <v>0</v>
@@ -28833,7 +28833,7 @@
         <v>1211</v>
       </c>
       <c r="B1213" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1213" t="n">
         <v>0</v>
@@ -28856,7 +28856,7 @@
         <v>1212</v>
       </c>
       <c r="B1214" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1214" t="n">
         <v>0</v>
@@ -28879,7 +28879,7 @@
         <v>1213</v>
       </c>
       <c r="B1215" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1215" t="n">
         <v>0</v>
@@ -28902,7 +28902,7 @@
         <v>1214</v>
       </c>
       <c r="B1216" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1216" t="n">
         <v>0</v>
@@ -28925,7 +28925,7 @@
         <v>1215</v>
       </c>
       <c r="B1217" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1217" t="n">
         <v>0</v>
@@ -28948,7 +28948,7 @@
         <v>1216</v>
       </c>
       <c r="B1218" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1218" t="n">
         <v>0</v>
@@ -28971,7 +28971,7 @@
         <v>1217</v>
       </c>
       <c r="B1219" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1219" t="n">
         <v>0</v>
@@ -28994,7 +28994,7 @@
         <v>1218</v>
       </c>
       <c r="B1220" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1220" t="n">
         <v>0</v>
@@ -29017,7 +29017,7 @@
         <v>1219</v>
       </c>
       <c r="B1221" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1221" t="n">
         <v>0</v>
@@ -29040,7 +29040,7 @@
         <v>1220</v>
       </c>
       <c r="B1222" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1222" t="n">
         <v>0</v>
@@ -29063,7 +29063,7 @@
         <v>1221</v>
       </c>
       <c r="B1223" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1223" t="n">
         <v>0</v>
@@ -29086,7 +29086,7 @@
         <v>1222</v>
       </c>
       <c r="B1224" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1224" t="n">
         <v>0</v>
@@ -29109,7 +29109,7 @@
         <v>1223</v>
       </c>
       <c r="B1225" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1225" t="n">
         <v>0</v>
@@ -29132,7 +29132,7 @@
         <v>1224</v>
       </c>
       <c r="B1226" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1226" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>1225</v>
       </c>
       <c r="B1227" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1227" t="n">
         <v>0</v>
@@ -29178,7 +29178,7 @@
         <v>1226</v>
       </c>
       <c r="B1228" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1228" t="n">
         <v>0</v>
@@ -29201,7 +29201,7 @@
         <v>1227</v>
       </c>
       <c r="B1229" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1229" t="n">
         <v>0</v>
@@ -29224,7 +29224,7 @@
         <v>1228</v>
       </c>
       <c r="B1230" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1230" t="n">
         <v>0</v>
@@ -29247,7 +29247,7 @@
         <v>1229</v>
       </c>
       <c r="B1231" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1231" t="n">
         <v>0</v>
@@ -29270,7 +29270,7 @@
         <v>1230</v>
       </c>
       <c r="B1232" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1232" t="n">
         <v>0</v>
@@ -29293,7 +29293,7 @@
         <v>1231</v>
       </c>
       <c r="B1233" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1233" t="n">
         <v>0</v>
@@ -29316,7 +29316,7 @@
         <v>1232</v>
       </c>
       <c r="B1234" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1234" t="n">
         <v>0</v>
@@ -29339,7 +29339,7 @@
         <v>1233</v>
       </c>
       <c r="B1235" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1235" t="n">
         <v>0</v>
@@ -29362,7 +29362,7 @@
         <v>1234</v>
       </c>
       <c r="B1236" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1236" t="n">
         <v>0</v>
@@ -29385,7 +29385,7 @@
         <v>1235</v>
       </c>
       <c r="B1237" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1237" t="n">
         <v>0</v>
@@ -29408,7 +29408,7 @@
         <v>1236</v>
       </c>
       <c r="B1238" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1238" t="n">
         <v>0</v>
@@ -29431,7 +29431,7 @@
         <v>1237</v>
       </c>
       <c r="B1239" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1239" t="n">
         <v>0</v>
@@ -29454,7 +29454,7 @@
         <v>1238</v>
       </c>
       <c r="B1240" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1240" t="n">
         <v>0</v>
@@ -29477,7 +29477,7 @@
         <v>1239</v>
       </c>
       <c r="B1241" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1241" t="n">
         <v>0</v>
@@ -29500,7 +29500,7 @@
         <v>1240</v>
       </c>
       <c r="B1242" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1242" t="n">
         <v>0</v>
@@ -29523,7 +29523,7 @@
         <v>1241</v>
       </c>
       <c r="B1243" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1243" t="n">
         <v>0</v>
@@ -29546,7 +29546,7 @@
         <v>1242</v>
       </c>
       <c r="B1244" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1244" t="n">
         <v>0</v>
@@ -29569,7 +29569,7 @@
         <v>1243</v>
       </c>
       <c r="B1245" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1245" t="n">
         <v>0</v>
@@ -29592,7 +29592,7 @@
         <v>1244</v>
       </c>
       <c r="B1246" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1246" t="n">
         <v>0</v>
@@ -29615,7 +29615,7 @@
         <v>1245</v>
       </c>
       <c r="B1247" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1247" t="n">
         <v>0</v>
@@ -29638,7 +29638,7 @@
         <v>1246</v>
       </c>
       <c r="B1248" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1248" t="n">
         <v>0</v>
@@ -29661,7 +29661,7 @@
         <v>1247</v>
       </c>
       <c r="B1249" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1249" t="n">
         <v>0</v>
@@ -29684,7 +29684,7 @@
         <v>1248</v>
       </c>
       <c r="B1250" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1250" t="n">
         <v>0</v>
@@ -29707,7 +29707,7 @@
         <v>1249</v>
       </c>
       <c r="B1251" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1251" t="n">
         <v>0</v>
@@ -29730,7 +29730,7 @@
         <v>1250</v>
       </c>
       <c r="B1252" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1252" t="n">
         <v>0</v>
@@ -29753,7 +29753,7 @@
         <v>1251</v>
       </c>
       <c r="B1253" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1253" t="n">
         <v>0</v>
@@ -29776,7 +29776,7 @@
         <v>1252</v>
       </c>
       <c r="B1254" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1254" t="n">
         <v>0</v>
@@ -29799,7 +29799,7 @@
         <v>1253</v>
       </c>
       <c r="B1255" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1255" t="n">
         <v>0</v>
@@ -29822,7 +29822,7 @@
         <v>1254</v>
       </c>
       <c r="B1256" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1256" t="n">
         <v>0</v>
@@ -29845,7 +29845,7 @@
         <v>1255</v>
       </c>
       <c r="B1257" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1257" t="n">
         <v>0</v>
@@ -29868,7 +29868,7 @@
         <v>1256</v>
       </c>
       <c r="B1258" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1258" t="n">
         <v>0</v>
@@ -29891,7 +29891,7 @@
         <v>1257</v>
       </c>
       <c r="B1259" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1259" t="n">
         <v>0</v>
@@ -29914,7 +29914,7 @@
         <v>1258</v>
       </c>
       <c r="B1260" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1260" t="n">
         <v>0</v>
@@ -29937,7 +29937,7 @@
         <v>1259</v>
       </c>
       <c r="B1261" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1261" t="n">
         <v>0</v>
@@ -29960,7 +29960,7 @@
         <v>1260</v>
       </c>
       <c r="B1262" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1262" t="n">
         <v>0</v>
@@ -29983,7 +29983,7 @@
         <v>1261</v>
       </c>
       <c r="B1263" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1263" t="n">
         <v>0</v>
@@ -30006,7 +30006,7 @@
         <v>1262</v>
       </c>
       <c r="B1264" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1264" t="n">
         <v>0</v>
@@ -30029,7 +30029,7 @@
         <v>1263</v>
       </c>
       <c r="B1265" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1265" t="n">
         <v>0</v>
@@ -30052,7 +30052,7 @@
         <v>1264</v>
       </c>
       <c r="B1266" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1266" t="n">
         <v>0</v>
@@ -30075,7 +30075,7 @@
         <v>1265</v>
       </c>
       <c r="B1267" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1267" t="n">
         <v>0</v>
@@ -30098,7 +30098,7 @@
         <v>1266</v>
       </c>
       <c r="B1268" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1268" t="n">
         <v>0</v>
@@ -30121,7 +30121,7 @@
         <v>1267</v>
       </c>
       <c r="B1269" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1269" t="n">
         <v>0</v>
@@ -30144,7 +30144,7 @@
         <v>1268</v>
       </c>
       <c r="B1270" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1270" t="n">
         <v>0</v>
@@ -30167,7 +30167,7 @@
         <v>1269</v>
       </c>
       <c r="B1271" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1271" t="n">
         <v>0</v>
@@ -30190,7 +30190,7 @@
         <v>1270</v>
       </c>
       <c r="B1272" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1272" t="n">
         <v>0</v>
@@ -30213,7 +30213,7 @@
         <v>1271</v>
       </c>
       <c r="B1273" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1273" t="n">
         <v>0</v>
@@ -30236,7 +30236,7 @@
         <v>1272</v>
       </c>
       <c r="B1274" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1274" t="n">
         <v>0</v>
@@ -30259,7 +30259,7 @@
         <v>1273</v>
       </c>
       <c r="B1275" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1275" t="n">
         <v>0</v>
@@ -30282,7 +30282,7 @@
         <v>1274</v>
       </c>
       <c r="B1276" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1276" t="n">
         <v>0</v>
@@ -30305,7 +30305,7 @@
         <v>1275</v>
       </c>
       <c r="B1277" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1277" t="n">
         <v>0</v>
@@ -30328,7 +30328,7 @@
         <v>1276</v>
       </c>
       <c r="B1278" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1278" t="n">
         <v>0</v>
@@ -30351,7 +30351,7 @@
         <v>1277</v>
       </c>
       <c r="B1279" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1279" t="n">
         <v>0</v>
@@ -30374,7 +30374,7 @@
         <v>1278</v>
       </c>
       <c r="B1280" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1280" t="n">
         <v>0</v>
@@ -30397,7 +30397,7 @@
         <v>1279</v>
       </c>
       <c r="B1281" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1281" t="n">
         <v>0</v>
@@ -30420,7 +30420,7 @@
         <v>1280</v>
       </c>
       <c r="B1282" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1282" t="n">
         <v>0</v>
@@ -30443,7 +30443,7 @@
         <v>1281</v>
       </c>
       <c r="B1283" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1283" t="n">
         <v>0</v>
@@ -30466,7 +30466,7 @@
         <v>1282</v>
       </c>
       <c r="B1284" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1284" t="n">
         <v>0</v>
@@ -30489,7 +30489,7 @@
         <v>1283</v>
       </c>
       <c r="B1285" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1285" t="n">
         <v>0</v>
@@ -30512,7 +30512,7 @@
         <v>1284</v>
       </c>
       <c r="B1286" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1286" t="n">
         <v>0</v>
@@ -30535,7 +30535,7 @@
         <v>1285</v>
       </c>
       <c r="B1287" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1287" t="n">
         <v>0</v>
@@ -30558,7 +30558,7 @@
         <v>1286</v>
       </c>
       <c r="B1288" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1288" t="n">
         <v>0</v>
@@ -30581,7 +30581,7 @@
         <v>1287</v>
       </c>
       <c r="B1289" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1289" t="n">
         <v>0</v>
@@ -30604,7 +30604,7 @@
         <v>1288</v>
       </c>
       <c r="B1290" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1290" t="n">
         <v>0</v>
@@ -30627,7 +30627,7 @@
         <v>1289</v>
       </c>
       <c r="B1291" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1291" t="n">
         <v>0</v>
@@ -30650,7 +30650,7 @@
         <v>1290</v>
       </c>
       <c r="B1292" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1292" t="n">
         <v>0</v>
@@ -30673,7 +30673,7 @@
         <v>1291</v>
       </c>
       <c r="B1293" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1293" t="n">
         <v>0</v>
@@ -30696,7 +30696,7 @@
         <v>1292</v>
       </c>
       <c r="B1294" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1294" t="n">
         <v>0</v>
@@ -30719,7 +30719,7 @@
         <v>1293</v>
       </c>
       <c r="B1295" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1295" t="n">
         <v>0</v>
@@ -30742,7 +30742,7 @@
         <v>1294</v>
       </c>
       <c r="B1296" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1296" t="n">
         <v>0</v>
@@ -30765,7 +30765,7 @@
         <v>1295</v>
       </c>
       <c r="B1297" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1297" t="n">
         <v>0</v>
@@ -30788,7 +30788,7 @@
         <v>1296</v>
       </c>
       <c r="B1298" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1298" t="n">
         <v>0</v>
@@ -30811,7 +30811,7 @@
         <v>1297</v>
       </c>
       <c r="B1299" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1299" t="n">
         <v>0</v>
@@ -30834,7 +30834,7 @@
         <v>1298</v>
       </c>
       <c r="B1300" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1300" t="n">
         <v>0</v>
@@ -30857,7 +30857,7 @@
         <v>1299</v>
       </c>
       <c r="B1301" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1301" t="n">
         <v>0</v>
@@ -30880,7 +30880,7 @@
         <v>1300</v>
       </c>
       <c r="B1302" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1302" t="n">
         <v>0</v>
@@ -30903,7 +30903,7 @@
         <v>1301</v>
       </c>
       <c r="B1303" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1303" t="n">
         <v>0</v>
@@ -30926,7 +30926,7 @@
         <v>1302</v>
       </c>
       <c r="B1304" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1304" t="n">
         <v>0</v>
@@ -30949,7 +30949,7 @@
         <v>1303</v>
       </c>
       <c r="B1305" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1305" t="n">
         <v>0</v>
@@ -30972,7 +30972,7 @@
         <v>1304</v>
       </c>
       <c r="B1306" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1306" t="n">
         <v>0</v>
@@ -30995,7 +30995,7 @@
         <v>1305</v>
       </c>
       <c r="B1307" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1307" t="n">
         <v>0</v>
@@ -31018,7 +31018,7 @@
         <v>1306</v>
       </c>
       <c r="B1308" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1308" t="n">
         <v>0</v>
@@ -31041,7 +31041,7 @@
         <v>1307</v>
       </c>
       <c r="B1309" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1309" t="n">
         <v>0</v>
@@ -31064,7 +31064,7 @@
         <v>1308</v>
       </c>
       <c r="B1310" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1310" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
         <v>1309</v>
       </c>
       <c r="B1311" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1311" t="n">
         <v>0</v>
@@ -31110,7 +31110,7 @@
         <v>1310</v>
       </c>
       <c r="B1312" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1312" t="n">
         <v>0</v>
@@ -31133,7 +31133,7 @@
         <v>1311</v>
       </c>
       <c r="B1313" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1313" t="n">
         <v>0</v>
@@ -31156,7 +31156,7 @@
         <v>1312</v>
       </c>
       <c r="B1314" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1314" t="n">
         <v>0</v>
@@ -31179,7 +31179,7 @@
         <v>1313</v>
       </c>
       <c r="B1315" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1315" t="n">
         <v>0</v>
@@ -31202,7 +31202,7 @@
         <v>1314</v>
       </c>
       <c r="B1316" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1316" t="n">
         <v>0</v>
@@ -31225,7 +31225,7 @@
         <v>1315</v>
       </c>
       <c r="B1317" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1317" t="n">
         <v>0</v>
@@ -31248,7 +31248,7 @@
         <v>1316</v>
       </c>
       <c r="B1318" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1318" t="n">
         <v>0</v>
@@ -31271,7 +31271,7 @@
         <v>1317</v>
       </c>
       <c r="B1319" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1319" t="n">
         <v>0</v>
@@ -31294,7 +31294,7 @@
         <v>1318</v>
       </c>
       <c r="B1320" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1320" t="n">
         <v>0</v>
@@ -31317,7 +31317,7 @@
         <v>1319</v>
       </c>
       <c r="B1321" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1321" t="n">
         <v>0</v>
@@ -31340,7 +31340,7 @@
         <v>1320</v>
       </c>
       <c r="B1322" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1322" t="n">
         <v>0</v>
@@ -31363,7 +31363,7 @@
         <v>1321</v>
       </c>
       <c r="B1323" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1323" t="n">
         <v>0</v>
@@ -31386,7 +31386,7 @@
         <v>1322</v>
       </c>
       <c r="B1324" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1324" t="n">
         <v>0</v>
@@ -31409,7 +31409,7 @@
         <v>1323</v>
       </c>
       <c r="B1325" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1325" t="n">
         <v>0</v>
@@ -31432,7 +31432,7 @@
         <v>1324</v>
       </c>
       <c r="B1326" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1326" t="n">
         <v>0</v>
@@ -31455,7 +31455,7 @@
         <v>1325</v>
       </c>
       <c r="B1327" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1327" t="n">
         <v>0</v>
@@ -31478,7 +31478,7 @@
         <v>1326</v>
       </c>
       <c r="B1328" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1328" t="n">
         <v>0</v>
@@ -31501,7 +31501,7 @@
         <v>1327</v>
       </c>
       <c r="B1329" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1329" t="n">
         <v>0</v>
@@ -31524,7 +31524,7 @@
         <v>1328</v>
       </c>
       <c r="B1330" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1330" t="n">
         <v>0</v>
@@ -31547,7 +31547,7 @@
         <v>1329</v>
       </c>
       <c r="B1331" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1331" t="n">
         <v>0</v>
@@ -31570,7 +31570,7 @@
         <v>1330</v>
       </c>
       <c r="B1332" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1332" t="n">
         <v>0</v>
@@ -31593,7 +31593,7 @@
         <v>1331</v>
       </c>
       <c r="B1333" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1333" t="n">
         <v>0</v>
@@ -31616,7 +31616,7 @@
         <v>1332</v>
       </c>
       <c r="B1334" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1334" t="n">
         <v>0</v>
@@ -31639,7 +31639,7 @@
         <v>1333</v>
       </c>
       <c r="B1335" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1335" t="n">
         <v>0</v>
@@ -31662,7 +31662,7 @@
         <v>1334</v>
       </c>
       <c r="B1336" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1336" t="n">
         <v>0</v>
@@ -31685,7 +31685,7 @@
         <v>1335</v>
       </c>
       <c r="B1337" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1337" t="n">
         <v>0</v>
@@ -31708,7 +31708,7 @@
         <v>1336</v>
       </c>
       <c r="B1338" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1338" t="n">
         <v>0</v>
@@ -31731,7 +31731,7 @@
         <v>1337</v>
       </c>
       <c r="B1339" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1339" t="n">
         <v>0</v>
@@ -31754,7 +31754,7 @@
         <v>1338</v>
       </c>
       <c r="B1340" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1340" t="n">
         <v>0</v>
@@ -31777,7 +31777,7 @@
         <v>1339</v>
       </c>
       <c r="B1341" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1341" t="n">
         <v>0</v>
@@ -31800,7 +31800,7 @@
         <v>1340</v>
       </c>
       <c r="B1342" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1342" t="n">
         <v>0</v>
@@ -31823,7 +31823,7 @@
         <v>1341</v>
       </c>
       <c r="B1343" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1343" t="n">
         <v>0</v>
@@ -31846,7 +31846,7 @@
         <v>1342</v>
       </c>
       <c r="B1344" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1344" t="n">
         <v>0</v>
@@ -31869,7 +31869,7 @@
         <v>1343</v>
       </c>
       <c r="B1345" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1345" t="n">
         <v>0</v>
@@ -31892,7 +31892,7 @@
         <v>1344</v>
       </c>
       <c r="B1346" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1346" t="n">
         <v>0</v>
@@ -31915,7 +31915,7 @@
         <v>1345</v>
       </c>
       <c r="B1347" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1347" t="n">
         <v>0</v>
@@ -31938,7 +31938,7 @@
         <v>1346</v>
       </c>
       <c r="B1348" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1348" t="n">
         <v>0</v>
@@ -31961,7 +31961,7 @@
         <v>1347</v>
       </c>
       <c r="B1349" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1349" t="n">
         <v>0</v>
@@ -31984,7 +31984,7 @@
         <v>1348</v>
       </c>
       <c r="B1350" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1350" t="n">
         <v>0</v>
@@ -32007,7 +32007,7 @@
         <v>1349</v>
       </c>
       <c r="B1351" t="n">
-        <v>677.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1351" t="n">
         <v>0</v>
@@ -32030,7 +32030,7 @@
         <v>1350</v>
       </c>
       <c r="B1352" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1352" t="n">
         <v>0</v>
@@ -32053,7 +32053,7 @@
         <v>1351</v>
       </c>
       <c r="B1353" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1353" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
         <v>1352</v>
       </c>
       <c r="B1354" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1354" t="n">
         <v>0</v>
@@ -32099,7 +32099,7 @@
         <v>1353</v>
       </c>
       <c r="B1355" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1355" t="n">
         <v>0</v>
@@ -32122,7 +32122,7 @@
         <v>1354</v>
       </c>
       <c r="B1356" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1356" t="n">
         <v>0</v>
@@ -32145,7 +32145,7 @@
         <v>1355</v>
       </c>
       <c r="B1357" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1357" t="n">
         <v>0</v>
@@ -32168,7 +32168,7 @@
         <v>1356</v>
       </c>
       <c r="B1358" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1358" t="n">
         <v>0</v>
@@ -32191,7 +32191,7 @@
         <v>1357</v>
       </c>
       <c r="B1359" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1359" t="n">
         <v>0</v>
@@ -32214,7 +32214,7 @@
         <v>1358</v>
       </c>
       <c r="B1360" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1360" t="n">
         <v>0</v>
@@ -32237,7 +32237,7 @@
         <v>1359</v>
       </c>
       <c r="B1361" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1361" t="n">
         <v>0</v>
@@ -32260,7 +32260,7 @@
         <v>1360</v>
       </c>
       <c r="B1362" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1362" t="n">
         <v>0</v>
@@ -32283,7 +32283,7 @@
         <v>1361</v>
       </c>
       <c r="B1363" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1363" t="n">
         <v>0</v>
@@ -32306,7 +32306,7 @@
         <v>1362</v>
       </c>
       <c r="B1364" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1364" t="n">
         <v>0</v>
@@ -32329,7 +32329,7 @@
         <v>1363</v>
       </c>
       <c r="B1365" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1365" t="n">
         <v>0</v>
@@ -32352,7 +32352,7 @@
         <v>1364</v>
       </c>
       <c r="B1366" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1366" t="n">
         <v>0</v>
@@ -32375,7 +32375,7 @@
         <v>1365</v>
       </c>
       <c r="B1367" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1367" t="n">
         <v>0</v>
@@ -32398,7 +32398,7 @@
         <v>1366</v>
       </c>
       <c r="B1368" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1368" t="n">
         <v>0</v>
@@ -32421,7 +32421,7 @@
         <v>1367</v>
       </c>
       <c r="B1369" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1369" t="n">
         <v>0</v>
@@ -32444,7 +32444,7 @@
         <v>1368</v>
       </c>
       <c r="B1370" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1370" t="n">
         <v>0</v>
@@ -32467,7 +32467,7 @@
         <v>1369</v>
       </c>
       <c r="B1371" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1371" t="n">
         <v>0</v>
@@ -32490,7 +32490,7 @@
         <v>1370</v>
       </c>
       <c r="B1372" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1372" t="n">
         <v>0</v>
@@ -32513,7 +32513,7 @@
         <v>1371</v>
       </c>
       <c r="B1373" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1373" t="n">
         <v>0</v>
@@ -32536,7 +32536,7 @@
         <v>1372</v>
       </c>
       <c r="B1374" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1374" t="n">
         <v>0</v>
@@ -32559,7 +32559,7 @@
         <v>1373</v>
       </c>
       <c r="B1375" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1375" t="n">
         <v>0</v>
@@ -32582,7 +32582,7 @@
         <v>1374</v>
       </c>
       <c r="B1376" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1376" t="n">
         <v>0</v>
@@ -32605,7 +32605,7 @@
         <v>1375</v>
       </c>
       <c r="B1377" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1377" t="n">
         <v>0</v>
@@ -32628,7 +32628,7 @@
         <v>1376</v>
       </c>
       <c r="B1378" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1378" t="n">
         <v>0</v>
@@ -32651,7 +32651,7 @@
         <v>1377</v>
       </c>
       <c r="B1379" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1379" t="n">
         <v>0</v>
@@ -32674,7 +32674,7 @@
         <v>1378</v>
       </c>
       <c r="B1380" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1380" t="n">
         <v>0</v>
@@ -32697,7 +32697,7 @@
         <v>1379</v>
       </c>
       <c r="B1381" t="n">
-        <v>655.5445736434111</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1381" t="n">
         <v>0</v>
@@ -32720,7 +32720,7 @@
         <v>1380</v>
       </c>
       <c r="B1382" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1382" t="n">
         <v>0</v>
@@ -32743,7 +32743,7 @@
         <v>1381</v>
       </c>
       <c r="B1383" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1383" t="n">
         <v>0</v>
@@ -32766,7 +32766,7 @@
         <v>1382</v>
       </c>
       <c r="B1384" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1384" t="n">
         <v>0</v>
@@ -32789,7 +32789,7 @@
         <v>1383</v>
       </c>
       <c r="B1385" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1385" t="n">
         <v>0</v>
@@ -32812,7 +32812,7 @@
         <v>1384</v>
       </c>
       <c r="B1386" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1386" t="n">
         <v>0</v>
@@ -32835,7 +32835,7 @@
         <v>1385</v>
       </c>
       <c r="B1387" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1387" t="n">
         <v>0</v>
@@ -32858,7 +32858,7 @@
         <v>1386</v>
       </c>
       <c r="B1388" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1388" t="n">
         <v>0</v>
@@ -32881,7 +32881,7 @@
         <v>1387</v>
       </c>
       <c r="B1389" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1389" t="n">
         <v>0</v>
@@ -32904,7 +32904,7 @@
         <v>1388</v>
       </c>
       <c r="B1390" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1390" t="n">
         <v>0</v>
@@ -32927,7 +32927,7 @@
         <v>1389</v>
       </c>
       <c r="B1391" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1391" t="n">
         <v>0</v>
@@ -32950,7 +32950,7 @@
         <v>1390</v>
       </c>
       <c r="B1392" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1392" t="n">
         <v>0</v>
@@ -32973,7 +32973,7 @@
         <v>1391</v>
       </c>
       <c r="B1393" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1393" t="n">
         <v>0</v>
@@ -32996,7 +32996,7 @@
         <v>1392</v>
       </c>
       <c r="B1394" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1394" t="n">
         <v>0</v>
@@ -33019,7 +33019,7 @@
         <v>1393</v>
       </c>
       <c r="B1395" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1395" t="n">
         <v>0</v>
@@ -33042,7 +33042,7 @@
         <v>1394</v>
       </c>
       <c r="B1396" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1396" t="n">
         <v>0</v>
@@ -33065,7 +33065,7 @@
         <v>1395</v>
       </c>
       <c r="B1397" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1397" t="n">
         <v>0</v>
@@ -33088,7 +33088,7 @@
         <v>1396</v>
       </c>
       <c r="B1398" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1398" t="n">
         <v>0</v>
@@ -33111,7 +33111,7 @@
         <v>1397</v>
       </c>
       <c r="B1399" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1399" t="n">
         <v>0</v>
@@ -33134,7 +33134,7 @@
         <v>1398</v>
       </c>
       <c r="B1400" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1400" t="n">
         <v>0</v>
@@ -33157,7 +33157,7 @@
         <v>1399</v>
       </c>
       <c r="B1401" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1401" t="n">
         <v>0</v>
@@ -33180,7 +33180,7 @@
         <v>1400</v>
       </c>
       <c r="B1402" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1402" t="n">
         <v>0</v>
@@ -33203,7 +33203,7 @@
         <v>1401</v>
       </c>
       <c r="B1403" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1403" t="n">
         <v>0</v>
@@ -33226,7 +33226,7 @@
         <v>1402</v>
       </c>
       <c r="B1404" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1404" t="n">
         <v>0</v>
@@ -33249,7 +33249,7 @@
         <v>1403</v>
       </c>
       <c r="B1405" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1405" t="n">
         <v>0</v>
@@ -33272,7 +33272,7 @@
         <v>1404</v>
       </c>
       <c r="B1406" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1406" t="n">
         <v>0</v>
@@ -33295,7 +33295,7 @@
         <v>1405</v>
       </c>
       <c r="B1407" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1407" t="n">
         <v>0</v>
@@ -33318,7 +33318,7 @@
         <v>1406</v>
       </c>
       <c r="B1408" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1408" t="n">
         <v>0</v>
@@ -33341,7 +33341,7 @@
         <v>1407</v>
       </c>
       <c r="B1409" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1409" t="n">
         <v>0</v>
@@ -33364,7 +33364,7 @@
         <v>1408</v>
       </c>
       <c r="B1410" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1410" t="n">
         <v>0</v>
@@ -33387,7 +33387,7 @@
         <v>1409</v>
       </c>
       <c r="B1411" t="n">
-        <v>0</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1411" t="n">
         <v>0</v>
@@ -33410,7 +33410,7 @@
         <v>1410</v>
       </c>
       <c r="B1412" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1412" t="n">
         <v>0</v>
@@ -33433,7 +33433,7 @@
         <v>1411</v>
       </c>
       <c r="B1413" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1413" t="n">
         <v>0</v>
@@ -33456,7 +33456,7 @@
         <v>1412</v>
       </c>
       <c r="B1414" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1414" t="n">
         <v>0</v>
@@ -33479,7 +33479,7 @@
         <v>1413</v>
       </c>
       <c r="B1415" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1415" t="n">
         <v>0</v>
@@ -33502,7 +33502,7 @@
         <v>1414</v>
       </c>
       <c r="B1416" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1416" t="n">
         <v>0</v>
@@ -33525,7 +33525,7 @@
         <v>1415</v>
       </c>
       <c r="B1417" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1417" t="n">
         <v>0</v>
@@ -33548,7 +33548,7 @@
         <v>1416</v>
       </c>
       <c r="B1418" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1418" t="n">
         <v>0</v>
@@ -33571,7 +33571,7 @@
         <v>1417</v>
       </c>
       <c r="B1419" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1419" t="n">
         <v>0</v>
@@ -33594,7 +33594,7 @@
         <v>1418</v>
       </c>
       <c r="B1420" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1420" t="n">
         <v>0</v>
@@ -33617,7 +33617,7 @@
         <v>1419</v>
       </c>
       <c r="B1421" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1421" t="n">
         <v>0</v>
@@ -33640,7 +33640,7 @@
         <v>1420</v>
       </c>
       <c r="B1422" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1422" t="n">
         <v>0</v>
@@ -33663,7 +33663,7 @@
         <v>1421</v>
       </c>
       <c r="B1423" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1423" t="n">
         <v>0</v>
@@ -33686,7 +33686,7 @@
         <v>1422</v>
       </c>
       <c r="B1424" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1424" t="n">
         <v>0</v>
@@ -33709,7 +33709,7 @@
         <v>1423</v>
       </c>
       <c r="B1425" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1425" t="n">
         <v>0</v>
@@ -33732,7 +33732,7 @@
         <v>1424</v>
       </c>
       <c r="B1426" t="n">
-        <v>631.2356321839079</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C1426" t="n">
         <v>0</v>
@@ -34131,7 +34131,7 @@
         <v>46130</v>
       </c>
       <c r="B2" t="n">
-        <v>827.1802721088436</v>
+        <v>1681.644557823129</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -34142,7 +34142,7 @@
         <v>46130.01041666666</v>
       </c>
       <c r="B3" t="n">
-        <v>761.1782555921625</v>
+        <v>1589.659268250391</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
@@ -34153,7 +34153,7 @@
         <v>46130.02083333334</v>
       </c>
       <c r="B4" t="n">
-        <v>787.9216784058756</v>
+        <v>1645.775660706761</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -34164,7 +34164,7 @@
         <v>46130.03125</v>
       </c>
       <c r="B5" t="n">
-        <v>325.9347826086956</v>
+        <v>675.6630434782609</v>
       </c>
       <c r="C5" t="n">
         <v>45</v>
@@ -34208,7 +34208,7 @@
         <v>46130.07291666666</v>
       </c>
       <c r="B9" t="n">
-        <v>11.1782555921623</v>
+        <v>14.65926825039015</v>
       </c>
       <c r="C9" t="n">
         <v>105</v>
@@ -34274,7 +34274,7 @@
         <v>46130.13541666666</v>
       </c>
       <c r="B15" t="n">
-        <v>1283.013605442177</v>
+        <v>2685.513605442177</v>
       </c>
       <c r="C15" t="n">
         <v>195</v>
@@ -34285,7 +34285,7 @@
         <v>46130.14583333334</v>
       </c>
       <c r="B16" t="n">
-        <v>998.0547945205479</v>
+        <v>2087.054794520548</v>
       </c>
       <c r="C16" t="n">
         <v>210</v>
@@ -34296,7 +34296,7 @@
         <v>46130.15625</v>
       </c>
       <c r="B17" t="n">
-        <v>623.0205479452055</v>
+        <v>1299.520547945205</v>
       </c>
       <c r="C17" t="n">
         <v>225</v>
@@ -34307,7 +34307,7 @@
         <v>46130.16666666666</v>
       </c>
       <c r="B18" t="n">
-        <v>1273.84999569448</v>
+        <v>2666.25505898562</v>
       </c>
       <c r="C18" t="n">
         <v>240</v>
@@ -34351,7 +34351,7 @@
         <v>46130.20833333334</v>
       </c>
       <c r="B22" t="n">
-        <v>638.3137446759526</v>
+        <v>1331.591055600323</v>
       </c>
       <c r="C22" t="n">
         <v>300</v>
@@ -34439,7 +34439,7 @@
         <v>46130.29166666666</v>
       </c>
       <c r="B30" t="n">
-        <v>1618.739243256291</v>
+        <v>1280.85378070122</v>
       </c>
       <c r="C30" t="n">
         <v>420</v>
@@ -34450,7 +34450,7 @@
         <v>46130.30208333334</v>
       </c>
       <c r="B31" t="n">
-        <v>447.674862428287</v>
+        <v>823.7432384966631</v>
       </c>
       <c r="C31" t="n">
         <v>435</v>
@@ -34461,7 +34461,7 @@
         <v>46130.3125</v>
       </c>
       <c r="B32" t="n">
-        <v>212.287953155946</v>
+        <v>328.3217084302076</v>
       </c>
       <c r="C32" t="n">
         <v>450</v>
@@ -34472,7 +34472,7 @@
         <v>46130.32291666666</v>
       </c>
       <c r="B33" t="n">
-        <v>258.1988603660643</v>
+        <v>424.5854149879131</v>
       </c>
       <c r="C33" t="n">
         <v>465</v>
@@ -34483,7 +34483,7 @@
         <v>46130.33333333334</v>
       </c>
       <c r="B34" t="n">
-        <v>351.8919635650871</v>
+        <v>622.2309466159345</v>
       </c>
       <c r="C34" t="n">
         <v>480</v>
@@ -34494,7 +34494,7 @@
         <v>46130.34375</v>
       </c>
       <c r="B35" t="n">
-        <v>212.0948211086065</v>
+        <v>328.1285763828681</v>
       </c>
       <c r="C35" t="n">
         <v>495</v>
@@ -34516,7 +34516,7 @@
         <v>46130.36458333334</v>
       </c>
       <c r="B37" t="n">
-        <v>108.9496169027165</v>
+        <v>113.6106338518691</v>
       </c>
       <c r="C37" t="n">
         <v>525</v>
@@ -34659,7 +34659,7 @@
         <v>46130.5</v>
       </c>
       <c r="B50" t="n">
-        <v>1000.155654408352</v>
+        <v>1767.517278024588</v>
       </c>
       <c r="C50" t="n">
         <v>720</v>
@@ -34670,7 +34670,7 @@
         <v>46130.51041666666</v>
       </c>
       <c r="B51" t="n">
-        <v>2228.946137566137</v>
+        <v>3016.175396825397</v>
       </c>
       <c r="C51" t="n">
         <v>735</v>
@@ -34681,7 +34681,7 @@
         <v>46130.52083333334</v>
       </c>
       <c r="B52" t="n">
-        <v>1096.860938887113</v>
+        <v>1974.082420368595</v>
       </c>
       <c r="C52" t="n">
         <v>750</v>
@@ -34692,7 +34692,7 @@
         <v>46130.53125</v>
       </c>
       <c r="B53" t="n">
-        <v>1096.547369441415</v>
+        <v>1967.969888525385</v>
       </c>
       <c r="C53" t="n">
         <v>765</v>
@@ -34703,7 +34703,7 @@
         <v>46130.54166666666</v>
       </c>
       <c r="B54" t="n">
-        <v>1091.852440944882</v>
+        <v>1967.452440944882</v>
       </c>
       <c r="C54" t="n">
         <v>780</v>
@@ -34714,7 +34714,7 @@
         <v>46130.55208333334</v>
       </c>
       <c r="B55" t="n">
-        <v>2854.142066954602</v>
+        <v>3812.773101437361</v>
       </c>
       <c r="C55" t="n">
         <v>795</v>
@@ -34725,7 +34725,7 @@
         <v>46130.5625</v>
       </c>
       <c r="B56" t="n">
-        <v>3339.601079893116</v>
+        <v>4274.230293376262</v>
       </c>
       <c r="C56" t="n">
         <v>810</v>
@@ -34736,7 +34736,7 @@
         <v>46130.57291666666</v>
       </c>
       <c r="B57" t="n">
-        <v>1360.028161620267</v>
+        <v>2076.802221770643</v>
       </c>
       <c r="C57" t="n">
         <v>825</v>
@@ -34747,7 +34747,7 @@
         <v>46130.58333333334</v>
       </c>
       <c r="B58" t="n">
-        <v>1042.346575342466</v>
+        <v>1786.606575342466</v>
       </c>
       <c r="C58" t="n">
         <v>840</v>
@@ -34758,7 +34758,7 @@
         <v>46130.59375</v>
       </c>
       <c r="B59" t="n">
-        <v>1061.258764049653</v>
+        <v>1905.469330087389</v>
       </c>
       <c r="C59" t="n">
         <v>855</v>
@@ -34769,7 +34769,7 @@
         <v>46130.60416666666</v>
       </c>
       <c r="B60" t="n">
-        <v>1081.059155358666</v>
+        <v>1874.992616897128</v>
       </c>
       <c r="C60" t="n">
         <v>870</v>
@@ -34780,7 +34780,7 @@
         <v>46130.61458333334</v>
       </c>
       <c r="B61" t="n">
-        <v>1128.89861329147</v>
+        <v>1975.031305599163</v>
       </c>
       <c r="C61" t="n">
         <v>885</v>
@@ -34967,7 +34967,7 @@
         <v>46130.79166666666</v>
       </c>
       <c r="B78" t="n">
-        <v>110.355337196607</v>
+        <v>134.9536911060721</v>
       </c>
       <c r="C78" t="n">
         <v>1140</v>
@@ -34978,7 +34978,7 @@
         <v>46130.80208333334</v>
       </c>
       <c r="B79" t="n">
-        <v>48.90827983622302</v>
+        <v>93.91492190264368</v>
       </c>
       <c r="C79" t="n">
         <v>1155</v>
@@ -34989,7 +34989,7 @@
         <v>46130.8125</v>
       </c>
       <c r="B80" t="n">
-        <v>92.57075088787417</v>
+        <v>185.6287138508371</v>
       </c>
       <c r="C80" t="n">
         <v>1170</v>
@@ -35000,7 +35000,7 @@
         <v>46130.82291666666</v>
       </c>
       <c r="B81" t="n">
-        <v>76.23886178459099</v>
+        <v>151.2499318952921</v>
       </c>
       <c r="C81" t="n">
         <v>1185</v>
@@ -35011,7 +35011,7 @@
         <v>46130.83333333334</v>
       </c>
       <c r="B82" t="n">
-        <v>513.5725921947727</v>
+        <v>1069.694960615825</v>
       </c>
       <c r="C82" t="n">
         <v>1200</v>
@@ -35022,7 +35022,7 @@
         <v>46130.84375</v>
       </c>
       <c r="B83" t="n">
-        <v>1014.308139534884</v>
+        <v>2121.247093023256</v>
       </c>
       <c r="C83" t="n">
         <v>1215</v>
@@ -35033,7 +35033,7 @@
         <v>46130.85416666666</v>
       </c>
       <c r="B84" t="n">
-        <v>753.5698317494937</v>
+        <v>1555.333381367815</v>
       </c>
       <c r="C84" t="n">
         <v>1230</v>
@@ -35044,7 +35044,7 @@
         <v>46130.86458333334</v>
       </c>
       <c r="B85" t="n">
-        <v>823.18522297808</v>
+        <v>1612.79985260771</v>
       </c>
       <c r="C85" t="n">
         <v>1245</v>
@@ -35055,7 +35055,7 @@
         <v>46130.875</v>
       </c>
       <c r="B86" t="n">
-        <v>825.8684424150175</v>
+        <v>1624.647701674277</v>
       </c>
       <c r="C86" t="n">
         <v>1260</v>
@@ -35066,7 +35066,7 @@
         <v>46130.88541666666</v>
       </c>
       <c r="B87" t="n">
-        <v>214.2295827669141</v>
+        <v>335.4143155913416</v>
       </c>
       <c r="C87" t="n">
         <v>1275</v>
@@ -35077,7 +35077,7 @@
         <v>46130.89583333334</v>
       </c>
       <c r="B88" t="n">
-        <v>690.215296035335</v>
+        <v>1332.621716268798</v>
       </c>
       <c r="C88" t="n">
         <v>1290</v>
@@ -35088,7 +35088,7 @@
         <v>46130.90625</v>
       </c>
       <c r="B89" t="n">
-        <v>425.7021078899861</v>
+        <v>777.751138897738</v>
       </c>
       <c r="C89" t="n">
         <v>1305</v>
@@ -35099,7 +35099,7 @@
         <v>46130.91666666666</v>
       </c>
       <c r="B90" t="n">
-        <v>482.3190843905129</v>
+        <v>896.9659955874241</v>
       </c>
       <c r="C90" t="n">
         <v>1320</v>
@@ -35110,7 +35110,7 @@
         <v>46130.92708333334</v>
       </c>
       <c r="B91" t="n">
-        <v>128.1547839424552</v>
+        <v>152.2613476490189</v>
       </c>
       <c r="C91" t="n">
         <v>1335</v>
@@ -35121,7 +35121,7 @@
         <v>46130.9375</v>
       </c>
       <c r="B92" t="n">
-        <v>783.2500530954659</v>
+        <v>1528.549084103218</v>
       </c>
       <c r="C92" t="n">
         <v>1350</v>
@@ -35132,7 +35132,7 @@
         <v>46130.94791666666</v>
       </c>
       <c r="B93" t="n">
-        <v>127.632009560581</v>
+        <v>151.6217779003493</v>
       </c>
       <c r="C93" t="n">
         <v>1365</v>
@@ -35143,7 +35143,7 @@
         <v>46130.95833333334</v>
       </c>
       <c r="B94" t="n">
-        <v>761.6738253440915</v>
+        <v>1482.772856351844</v>
       </c>
       <c r="C94" t="n">
         <v>1380</v>
@@ -35154,7 +35154,7 @@
         <v>46130.96875</v>
       </c>
       <c r="B95" t="n">
-        <v>128.5534193684879</v>
+        <v>152.7067012217697</v>
       </c>
       <c r="C95" t="n">
         <v>1395</v>
@@ -35165,7 +35165,7 @@
         <v>46130.97916666666</v>
       </c>
       <c r="B96" t="n">
-        <v>128.9794520547945</v>
+        <v>153.1794520547945</v>
       </c>
       <c r="C96" t="n">
         <v>1410</v>
@@ -35176,7 +35176,7 @@
         <v>46130.98958333334</v>
       </c>
       <c r="B97" t="n">
-        <v>738.3444757213229</v>
+        <v>1432.703671123622</v>
       </c>
       <c r="C97" t="n">
         <v>1425</v>
@@ -35193,7 +35193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35233,7 +35233,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>782.1509253948951</v>
+        <v>1278.953957287405</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -35277,7 +35277,7 @@
         <v>45</v>
       </c>
       <c r="B4" t="n">
-        <v>-782.1509253948951</v>
+        <v>-1278.953957287405</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -35288,7 +35288,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5866131940461713</v>
+        <v>0.9592154679655538</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -35299,7 +35299,7 @@
         <v>180</v>
       </c>
       <c r="B5" t="n">
-        <v>1036.455696202532</v>
+        <v>2176.556962025316</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -35321,7 +35321,7 @@
         <v>240</v>
       </c>
       <c r="B6" t="n">
-        <v>-1036.455696202532</v>
+        <v>-2176.556962025316</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -35332,7 +35332,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.036455696202532</v>
+        <v>2.176556962025316</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -35343,7 +35343,7 @@
         <v>285</v>
       </c>
       <c r="B7" t="n">
-        <v>630.2521008403362</v>
+        <v>1323.529411764706</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -35365,7 +35365,7 @@
         <v>300</v>
       </c>
       <c r="B8" t="n">
-        <v>-630.2521008403362</v>
+        <v>-1323.529411764706</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -35376,7 +35376,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.1575630252100841</v>
+        <v>0.3308823529411765</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -35409,7 +35409,7 @@
         <v>405</v>
       </c>
       <c r="B10" t="n">
-        <v>410.1478729900802</v>
+        <v>527.9771999458344</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -35431,7 +35431,7 @@
         <v>495</v>
       </c>
       <c r="B11" t="n">
-        <v>-410.1478729900802</v>
+        <v>-527.9771999458344</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -35442,7 +35442,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6152218094851203</v>
+        <v>0.7919657999187516</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -35519,7 +35519,7 @@
         <v>704</v>
       </c>
       <c r="B15" t="n">
-        <v>758.8943872303877</v>
+        <v>1593.678213183814</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -35607,7 +35607,7 @@
         <v>884</v>
       </c>
       <c r="B19" t="n">
-        <v>-758.8943872303877</v>
+        <v>-1593.678213183814</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -35618,7 +35618,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.276683161691163</v>
+        <v>4.781034639551442</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -35758,10 +35758,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1139</v>
+        <v>1125</v>
       </c>
       <c r="B26" t="n">
-        <v>439.1349644560054</v>
+        <v>771.1187358044058</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -35824,10 +35824,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1320</v>
+        <v>1425</v>
       </c>
       <c r="B29" t="n">
-        <v>-439.1349644560054</v>
+        <v>-771.1187358044058</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -35838,141 +35838,9 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.324723809442283</v>
+        <v>3.855593679022029</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>1335</v>
-      </c>
-      <c r="B30" t="n">
-        <v>677.5445736434111</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1350</v>
-      </c>
-      <c r="B31" t="n">
-        <v>-677.5445736434111</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0.1693861434108528</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>1365</v>
-      </c>
-      <c r="B32" t="n">
-        <v>655.5445736434111</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>1380</v>
-      </c>
-      <c r="B33" t="n">
-        <v>-655.5445736434111</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0.1638861434108528</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>1410</v>
-      </c>
-      <c r="B34" t="n">
-        <v>631.2356321839079</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>1425</v>
-      </c>
-      <c r="B35" t="n">
-        <v>-631.2356321839079</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>0.157808908045977</v>
-      </c>
-      <c r="F35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -35987,7 +35855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH35"/>
+  <dimension ref="A1:AB29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36075,24 +35943,6 @@
       <c r="AB1" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="n">
-        <v>33</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -36179,24 +36029,6 @@
       <c r="AB2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -36281,24 +36113,6 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36387,24 +36201,6 @@
       <c r="AB4" t="n">
         <v>0</v>
       </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -36491,24 +36287,6 @@
       <c r="AB5" t="n">
         <v>0</v>
       </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -36595,24 +36373,6 @@
       <c r="AB6" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -36699,24 +36459,6 @@
       <c r="AB7" t="n">
         <v>0</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -36803,24 +36545,6 @@
       <c r="AB8" t="n">
         <v>0</v>
       </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -36907,24 +36631,6 @@
       <c r="AB9" t="n">
         <v>0</v>
       </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -37011,24 +36717,6 @@
       <c r="AB10" t="n">
         <v>0</v>
       </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -37115,24 +36803,6 @@
       <c r="AB11" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -37219,24 +36889,6 @@
       <c r="AB12" t="n">
         <v>0</v>
       </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -37323,24 +36975,6 @@
       <c r="AB13" t="n">
         <v>0</v>
       </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -37427,24 +37061,6 @@
       <c r="AB14" t="n">
         <v>0</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -37531,24 +37147,6 @@
       <c r="AB15" t="n">
         <v>0</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -37635,24 +37233,6 @@
       <c r="AB16" t="n">
         <v>0</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -37739,24 +37319,6 @@
       <c r="AB17" t="n">
         <v>0</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -37843,24 +37405,6 @@
       <c r="AB18" t="n">
         <v>0</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -37947,24 +37491,6 @@
       <c r="AB19" t="n">
         <v>0</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -38051,24 +37577,6 @@
       <c r="AB20" t="n">
         <v>0</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -38155,24 +37663,6 @@
       <c r="AB21" t="n">
         <v>0</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -38259,24 +37749,6 @@
       <c r="AB22" t="n">
         <v>0</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -38363,24 +37835,6 @@
       <c r="AB23" t="n">
         <v>0</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -38467,24 +37921,6 @@
       <c r="AB24" t="n">
         <v>0</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -38571,24 +38007,6 @@
       <c r="AB25" t="n">
         <v>0</v>
       </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -38675,24 +38093,6 @@
       <c r="AB26" t="n">
         <v>1</v>
       </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -38779,24 +38179,6 @@
       <c r="AB27" t="n">
         <v>0</v>
       </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -38883,24 +38265,6 @@
       <c r="AB28" t="n">
         <v>0</v>
       </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -38985,648 +38349,6 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>0</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>0</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>0</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>0</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>0</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>0</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH35" t="n">
         <v>1</v>
       </c>
     </row>
